--- a/CodingProblemsSheet.xlsx
+++ b/CodingProblemsSheet.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1966" uniqueCount="1027">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2019" uniqueCount="1030">
   <si>
     <t>Curious freaks CODING SHEET by Nandhini</t>
   </si>
@@ -519,6 +519,9 @@
     <t>Learn what is map and how its represented before moving forward</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>Count frequency of elements in array(Solve efficiently, try applying what you learnt about map)</t>
   </si>
   <si>
@@ -549,6 +552,9 @@
     <t>https://leetcode.com/problems/4sum/</t>
   </si>
   <si>
+    <t>LeetCode</t>
+  </si>
+  <si>
     <t>Find triplets with zero sum</t>
   </si>
   <si>
@@ -595,6 +601,9 @@
   </si>
   <si>
     <t>https://www.geeksforgeeks.org/problems/trapping-rain-water-1587115621/1?itm_source=geeksforgeeks&amp;itm_medium=Article&amp;itm_campaign=bottom_sticky_on_Article</t>
+  </si>
+  <si>
+    <t>Hard</t>
   </si>
   <si>
     <t>Must Solve</t>
@@ -4012,7 +4021,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="99">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4141,6 +4150,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="14" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="13" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="21" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
@@ -4604,17 +4622,17 @@
   <dimension ref="A1:K1506"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="93" width="32.14785714285715" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="93" width="72.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="93" width="56.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="93" width="24.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="93" width="20.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="94" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="94" width="13.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="93" width="20.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="93" width="53.14785714285715" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="95" width="45.14785714285715" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="95" width="23.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="96" width="32.14785714285715" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="96" width="72.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="96" width="56.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="96" width="24.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="96" width="20.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="97" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="97" width="13.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="96" width="20.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="96" width="53.14785714285715" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="98" width="45.14785714285715" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="98" width="23.719285714285714" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="27" customFormat="1" s="1">
@@ -5281,7 +5299,9 @@
       <c r="F32" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G32" s="4"/>
+      <c r="G32" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="H32" s="32" t="s">
         <v>30</v>
       </c>
@@ -5308,7 +5328,9 @@
       <c r="F33" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G33" s="4"/>
+      <c r="G33" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="H33" s="32" t="s">
         <v>74</v>
       </c>
@@ -5335,7 +5357,9 @@
       <c r="F34" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G34" s="4"/>
+      <c r="G34" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="H34" s="32" t="s">
         <v>30</v>
       </c>
@@ -5362,7 +5386,9 @@
       <c r="F35" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G35" s="4"/>
+      <c r="G35" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="H35" s="32" t="s">
         <v>30</v>
       </c>
@@ -5416,7 +5442,9 @@
       <c r="F37" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G37" s="4"/>
+      <c r="G37" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="H37" s="32" t="s">
         <v>30</v>
       </c>
@@ -5445,7 +5473,9 @@
       <c r="F38" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G38" s="4"/>
+      <c r="G38" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="H38" s="32" t="s">
         <v>30</v>
       </c>
@@ -5474,7 +5504,9 @@
       <c r="F39" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G39" s="4"/>
+      <c r="G39" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="H39" s="32" t="s">
         <v>30</v>
       </c>
@@ -5500,9 +5532,15 @@
       <c r="E40" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="32"/>
+      <c r="F40" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H40" s="32" t="s">
+        <v>30</v>
+      </c>
       <c r="I40" s="32"/>
       <c r="J40" s="11"/>
       <c r="K40" s="11"/>
@@ -5521,9 +5559,15 @@
       <c r="E41" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="32"/>
+      <c r="F41" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H41" s="32" t="s">
+        <v>30</v>
+      </c>
       <c r="I41" s="32"/>
       <c r="J41" s="11"/>
       <c r="K41" s="11"/>
@@ -5540,9 +5584,15 @@
       <c r="E42" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="32"/>
+      <c r="F42" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G42" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="H42" s="45" t="s">
+        <v>103</v>
+      </c>
       <c r="I42" s="32"/>
       <c r="J42" s="11"/>
       <c r="K42" s="11"/>
@@ -5550,10 +5600,10 @@
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="29"/>
       <c r="B43" s="30" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C43" s="30" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D43" s="43" t="s">
         <v>26</v>
@@ -5561,26 +5611,34 @@
       <c r="E43" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="32"/>
+      <c r="F43" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H43" s="32" t="s">
+        <v>30</v>
+      </c>
       <c r="I43" s="32"/>
       <c r="J43" s="11"/>
       <c r="K43" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A44" s="29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B44" s="29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C44" s="30"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
+      <c r="H44" s="46" t="s">
+        <v>103</v>
+      </c>
       <c r="I44" s="3"/>
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
@@ -5588,10 +5646,10 @@
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="30"/>
       <c r="B45" s="30" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C45" s="30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D45" s="30" t="s">
         <v>26</v>
@@ -5599,20 +5657,26 @@
       <c r="E45" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="44"/>
-      <c r="I45" s="44"/>
+      <c r="F45" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H45" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="I45" s="47"/>
       <c r="J45" s="11"/>
       <c r="K45" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="30"/>
       <c r="B46" s="30" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C46" s="30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D46" s="35" t="s">
         <v>26</v>
@@ -5620,9 +5684,15 @@
       <c r="E46" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="32"/>
+      <c r="F46" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H46" s="32" t="s">
+        <v>30</v>
+      </c>
       <c r="I46" s="32"/>
       <c r="J46" s="11"/>
       <c r="K46" s="11"/>
@@ -5630,10 +5700,10 @@
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="30"/>
       <c r="B47" s="30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C47" s="30" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D47" s="35" t="s">
         <v>26</v>
@@ -5641,9 +5711,15 @@
       <c r="E47" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="32"/>
+      <c r="F47" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H47" s="32" t="s">
+        <v>30</v>
+      </c>
       <c r="I47" s="32"/>
       <c r="J47" s="11"/>
       <c r="K47" s="11"/>
@@ -5651,10 +5727,10 @@
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="30"/>
       <c r="B48" s="30" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C48" s="30" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D48" s="35" t="s">
         <v>26</v>
@@ -5662,9 +5738,15 @@
       <c r="E48" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="32"/>
+      <c r="F48" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H48" s="32" t="s">
+        <v>30</v>
+      </c>
       <c r="I48" s="32"/>
       <c r="J48" s="11"/>
       <c r="K48" s="11"/>
@@ -5672,10 +5754,10 @@
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="30"/>
       <c r="B49" s="30" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C49" s="30" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D49" s="35" t="s">
         <v>26</v>
@@ -5683,9 +5765,15 @@
       <c r="E49" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="32"/>
+      <c r="F49" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H49" s="32" t="s">
+        <v>30</v>
+      </c>
       <c r="I49" s="32"/>
       <c r="J49" s="11"/>
       <c r="K49" s="11"/>
@@ -5693,10 +5781,10 @@
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="30"/>
       <c r="B50" s="30" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C50" s="30" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D50" s="35" t="s">
         <v>26</v>
@@ -5704,9 +5792,15 @@
       <c r="E50" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="32"/>
+      <c r="F50" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H50" s="32" t="s">
+        <v>30</v>
+      </c>
       <c r="I50" s="32"/>
       <c r="J50" s="11"/>
       <c r="K50" s="11"/>
@@ -5714,10 +5808,10 @@
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="30"/>
       <c r="B51" s="30" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C51" s="30" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D51" s="35" t="s">
         <v>26</v>
@@ -5725,9 +5819,15 @@
       <c r="E51" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="32"/>
+      <c r="F51" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H51" s="32" t="s">
+        <v>30</v>
+      </c>
       <c r="I51" s="32"/>
       <c r="J51" s="11"/>
       <c r="K51" s="11"/>
@@ -5735,10 +5835,10 @@
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="30"/>
       <c r="B52" s="30" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C52" s="30" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D52" s="35" t="s">
         <v>26</v>
@@ -5746,9 +5846,15 @@
       <c r="E52" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="32"/>
+      <c r="F52" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H52" s="32" t="s">
+        <v>30</v>
+      </c>
       <c r="I52" s="32"/>
       <c r="J52" s="11"/>
       <c r="K52" s="11"/>
@@ -5756,10 +5862,10 @@
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="30"/>
       <c r="B53" s="30" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C53" s="30" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D53" s="43" t="s">
         <v>26</v>
@@ -5767,9 +5873,15 @@
       <c r="E53" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="32"/>
+      <c r="F53" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H53" s="32" t="s">
+        <v>30</v>
+      </c>
       <c r="I53" s="32"/>
       <c r="J53" s="11"/>
       <c r="K53" s="11"/>
@@ -5777,10 +5889,10 @@
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="30"/>
       <c r="B54" s="30" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C54" s="30" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D54" s="35" t="s">
         <v>26</v>
@@ -5788,9 +5900,15 @@
       <c r="E54" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="32"/>
+      <c r="F54" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H54" s="32" t="s">
+        <v>30</v>
+      </c>
       <c r="I54" s="32"/>
       <c r="J54" s="11"/>
       <c r="K54" s="11"/>
@@ -5798,10 +5916,10 @@
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="30"/>
       <c r="B55" s="30" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C55" s="30" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D55" s="35" t="s">
         <v>26</v>
@@ -5809,16 +5927,22 @@
       <c r="E55" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
-      <c r="H55" s="32"/>
+      <c r="F55" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="H55" s="32" t="s">
+        <v>30</v>
+      </c>
       <c r="I55" s="32"/>
       <c r="J55" s="11"/>
       <c r="K55" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A56" s="29" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B56" s="30"/>
       <c r="C56" s="30"/>
@@ -5834,10 +5958,10 @@
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="30"/>
       <c r="B57" s="30" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C57" s="30" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D57" s="30" t="s">
         <v>26</v>
@@ -5847,18 +5971,18 @@
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
-      <c r="H57" s="44"/>
-      <c r="I57" s="44"/>
+      <c r="H57" s="47"/>
+      <c r="I57" s="47"/>
       <c r="J57" s="11"/>
       <c r="K57" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="30"/>
       <c r="B58" s="30" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C58" s="30" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D58" s="35" t="s">
         <v>26</v>
@@ -5876,10 +6000,10 @@
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="30"/>
       <c r="B59" s="30" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C59" s="30" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D59" s="35" t="s">
         <v>26</v>
@@ -5897,10 +6021,10 @@
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="30"/>
       <c r="B60" s="30" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C60" s="30" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D60" s="35" t="s">
         <v>26</v>
@@ -5918,10 +6042,10 @@
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="30"/>
       <c r="B61" s="30" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C61" s="30" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D61" s="35" t="s">
         <v>26</v>
@@ -5939,10 +6063,10 @@
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="30"/>
       <c r="B62" s="30" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C62" s="30" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D62" s="35" t="s">
         <v>26</v>
@@ -5958,32 +6082,32 @@
       <c r="K62" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
-      <c r="A63" s="45"/>
-      <c r="B63" s="45" t="s">
-        <v>142</v>
-      </c>
-      <c r="C63" s="46" t="s">
-        <v>143</v>
+      <c r="A63" s="48"/>
+      <c r="B63" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="C63" s="49" t="s">
+        <v>146</v>
       </c>
       <c r="D63" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="E63" s="47" t="s">
+      <c r="E63" s="50" t="s">
         <v>27</v>
       </c>
       <c r="F63" s="4"/>
       <c r="G63" s="4"/>
-      <c r="H63" s="48"/>
-      <c r="I63" s="48"/>
+      <c r="H63" s="51"/>
+      <c r="I63" s="51"/>
       <c r="J63" s="11"/>
       <c r="K63" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A64" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="B64" s="49" t="s">
-        <v>145</v>
+        <v>147</v>
+      </c>
+      <c r="B64" s="52" t="s">
+        <v>148</v>
       </c>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
@@ -5997,13 +6121,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="24" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B65" s="25" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C65" s="25"/>
-      <c r="D65" s="50"/>
+      <c r="D65" s="53"/>
       <c r="E65" s="26"/>
       <c r="F65" s="4"/>
       <c r="G65" s="4"/>
@@ -6014,7 +6138,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A66" s="29" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B66" s="30"/>
       <c r="C66" s="30"/>
@@ -6030,7 +6154,7 @@
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="30"/>
       <c r="B67" s="30" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C67" s="30"/>
       <c r="D67" s="30" t="s">
@@ -6041,18 +6165,18 @@
       </c>
       <c r="F67" s="4"/>
       <c r="G67" s="4"/>
-      <c r="H67" s="44"/>
-      <c r="I67" s="44"/>
+      <c r="H67" s="47"/>
+      <c r="I67" s="47"/>
       <c r="J67" s="11"/>
       <c r="K67" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="30"/>
       <c r="B68" s="30" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C68" s="30" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D68" s="35" t="s">
         <v>26</v>
@@ -6070,10 +6194,10 @@
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="30"/>
       <c r="B69" s="30" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C69" s="30" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D69" s="35" t="s">
         <v>26</v>
@@ -6091,10 +6215,10 @@
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="30"/>
       <c r="B70" s="30" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C70" s="30" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D70" s="35" t="s">
         <v>26</v>
@@ -6112,10 +6236,10 @@
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="30"/>
       <c r="B71" s="30" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C71" s="30" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D71" s="35" t="s">
         <v>26</v>
@@ -6133,10 +6257,10 @@
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="30"/>
       <c r="B72" s="30" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C72" s="30" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D72" s="43" t="s">
         <v>26</v>
@@ -6154,10 +6278,10 @@
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="30"/>
       <c r="B73" s="30" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C73" s="30" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D73" s="35" t="s">
         <v>26</v>
@@ -6174,13 +6298,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="B74" s="51" t="s">
-        <v>163</v>
+        <v>165</v>
+      </c>
+      <c r="B74" s="54" t="s">
+        <v>166</v>
       </c>
       <c r="C74" s="25"/>
-      <c r="D74" s="50"/>
+      <c r="D74" s="53"/>
       <c r="E74" s="26"/>
       <c r="F74" s="4"/>
       <c r="G74" s="4"/>
@@ -6194,7 +6318,7 @@
         <v>18</v>
       </c>
       <c r="B75" s="30" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C75" s="30"/>
       <c r="D75" s="35" t="s">
@@ -6205,18 +6329,18 @@
       </c>
       <c r="F75" s="4"/>
       <c r="G75" s="4"/>
-      <c r="H75" s="44"/>
-      <c r="I75" s="44"/>
+      <c r="H75" s="47"/>
+      <c r="I75" s="47"/>
       <c r="J75" s="11"/>
       <c r="K75" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="29"/>
       <c r="B76" s="30" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C76" s="30" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D76" s="35" t="s">
         <v>26</v>
@@ -6234,10 +6358,10 @@
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="29"/>
       <c r="B77" s="30" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C77" s="30" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D77" s="35" t="s">
         <v>26</v>
@@ -6253,33 +6377,33 @@
       <c r="K77" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
-      <c r="A78" s="52"/>
-      <c r="B78" s="45" t="s">
-        <v>169</v>
-      </c>
-      <c r="C78" s="53" t="s">
-        <v>170</v>
+      <c r="A78" s="55"/>
+      <c r="B78" s="48" t="s">
+        <v>172</v>
+      </c>
+      <c r="C78" s="56" t="s">
+        <v>173</v>
       </c>
       <c r="D78" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="E78" s="54" t="s">
+      <c r="E78" s="57" t="s">
         <v>27</v>
       </c>
       <c r="F78" s="4"/>
       <c r="G78" s="4"/>
-      <c r="H78" s="55"/>
-      <c r="I78" s="55"/>
+      <c r="H78" s="58"/>
+      <c r="I78" s="58"/>
       <c r="J78" s="11"/>
       <c r="K78" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="29"/>
       <c r="B79" s="30" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C79" s="30" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D79" s="30" t="s">
         <v>26</v>
@@ -6289,24 +6413,24 @@
       </c>
       <c r="F79" s="4"/>
       <c r="G79" s="4"/>
-      <c r="H79" s="44"/>
-      <c r="I79" s="44"/>
+      <c r="H79" s="47"/>
+      <c r="I79" s="47"/>
       <c r="J79" s="11"/>
       <c r="K79" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="29"/>
       <c r="B80" s="30" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C80" s="30" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D80" s="35" t="s">
         <v>26</v>
       </c>
       <c r="E80" s="31" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F80" s="4"/>
       <c r="G80" s="4"/>
@@ -6318,16 +6442,16 @@
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="29"/>
       <c r="B81" s="30" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C81" s="30" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D81" s="35" t="s">
         <v>26</v>
       </c>
       <c r="E81" s="31" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F81" s="4"/>
       <c r="G81" s="4"/>
@@ -6339,16 +6463,16 @@
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="29"/>
       <c r="B82" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="C82" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="D82" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="E82" s="31" t="s">
         <v>178</v>
-      </c>
-      <c r="C82" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="D82" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="E82" s="31" t="s">
-        <v>175</v>
       </c>
       <c r="F82" s="4"/>
       <c r="G82" s="4"/>
@@ -6359,13 +6483,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="24" t="s">
-        <v>180</v>
-      </c>
-      <c r="B83" s="56" t="s">
-        <v>181</v>
+        <v>183</v>
+      </c>
+      <c r="B83" s="59" t="s">
+        <v>184</v>
       </c>
       <c r="C83" s="25"/>
-      <c r="D83" s="50"/>
+      <c r="D83" s="53"/>
       <c r="E83" s="26"/>
       <c r="F83" s="4"/>
       <c r="G83" s="4"/>
@@ -6376,7 +6500,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A84" s="29" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B84" s="30"/>
       <c r="C84" s="30"/>
@@ -6392,10 +6516,10 @@
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="30"/>
       <c r="B85" s="30" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C85" s="30" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D85" s="35" t="s">
         <v>26</v>
@@ -6413,10 +6537,10 @@
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="30"/>
       <c r="B86" s="30" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C86" s="30" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D86" s="35" t="s">
         <v>26</v>
@@ -6434,10 +6558,10 @@
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="30"/>
       <c r="B87" s="30" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C87" s="30" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D87" s="35" t="s">
         <v>26</v>
@@ -6455,10 +6579,10 @@
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="30"/>
       <c r="B88" s="30" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C88" s="30" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D88" s="35" t="s">
         <v>26</v>
@@ -6476,10 +6600,10 @@
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="30"/>
       <c r="B89" s="30" t="s">
-        <v>191</v>
-      </c>
-      <c r="C89" s="57" t="s">
-        <v>192</v>
+        <v>194</v>
+      </c>
+      <c r="C89" s="60" t="s">
+        <v>195</v>
       </c>
       <c r="D89" s="35" t="s">
         <v>26</v>
@@ -6497,10 +6621,10 @@
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="30"/>
       <c r="B90" s="30" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C90" s="30" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D90" s="35" t="s">
         <v>26</v>
@@ -6517,7 +6641,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A91" s="29" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B91" s="30"/>
       <c r="C91" s="30"/>
@@ -6533,16 +6657,16 @@
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="29"/>
       <c r="B92" s="30" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C92" s="30" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D92" s="35" t="s">
         <v>26</v>
       </c>
       <c r="E92" s="31" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F92" s="4"/>
       <c r="G92" s="4"/>
@@ -6554,16 +6678,16 @@
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="29"/>
       <c r="B93" s="30" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C93" s="30" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D93" s="35" t="s">
         <v>26</v>
       </c>
       <c r="E93" s="31" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F93" s="4"/>
       <c r="G93" s="4"/>
@@ -6575,16 +6699,16 @@
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="29"/>
       <c r="B94" s="30" t="s">
+        <v>204</v>
+      </c>
+      <c r="C94" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="D94" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="E94" s="31" t="s">
         <v>201</v>
-      </c>
-      <c r="C94" s="30" t="s">
-        <v>202</v>
-      </c>
-      <c r="D94" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="E94" s="31" t="s">
-        <v>198</v>
       </c>
       <c r="F94" s="4"/>
       <c r="G94" s="4"/>
@@ -6596,14 +6720,14 @@
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
       <c r="A95" s="29"/>
       <c r="B95" s="30" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C95" s="30"/>
       <c r="D95" s="43" t="s">
         <v>26</v>
       </c>
       <c r="E95" s="31" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F95" s="4"/>
       <c r="G95" s="4"/>
@@ -6614,7 +6738,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
       <c r="A96" s="29" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B96" s="30"/>
       <c r="C96" s="30"/>
@@ -6630,16 +6754,16 @@
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
       <c r="A97" s="29"/>
       <c r="B97" s="30" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C97" s="30" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D97" s="35" t="s">
         <v>26</v>
       </c>
       <c r="E97" s="31" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F97" s="4"/>
       <c r="G97" s="4"/>
@@ -6651,16 +6775,16 @@
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
       <c r="A98" s="29"/>
       <c r="B98" s="30" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C98" s="30" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D98" s="35" t="s">
         <v>26</v>
       </c>
       <c r="E98" s="31" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F98" s="4"/>
       <c r="G98" s="4"/>
@@ -6671,7 +6795,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A99" s="29" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B99" s="30"/>
       <c r="C99" s="30"/>
@@ -6687,10 +6811,10 @@
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
       <c r="A100" s="13"/>
       <c r="B100" s="30" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C100" s="30" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D100" s="35" t="s">
         <v>26</v>
@@ -6708,10 +6832,10 @@
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
       <c r="A101" s="13"/>
       <c r="B101" s="30" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C101" s="30" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D101" s="35" t="s">
         <v>26</v>
@@ -6729,10 +6853,10 @@
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
       <c r="A102" s="13"/>
       <c r="B102" s="30" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C102" s="30" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D102" s="35" t="s">
         <v>26</v>
@@ -6750,10 +6874,10 @@
     <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
       <c r="A103" s="13"/>
       <c r="B103" s="30" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C103" s="30" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D103" s="35" t="s">
         <v>26</v>
@@ -6769,8 +6893,8 @@
       <c r="K103" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75">
-      <c r="A104" s="58" t="s">
-        <v>218</v>
+      <c r="A104" s="61" t="s">
+        <v>221</v>
       </c>
       <c r="B104" s="30"/>
       <c r="C104" s="30"/>
@@ -6788,10 +6912,10 @@
     <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75">
       <c r="A105" s="13"/>
       <c r="B105" s="30" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C105" s="30" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D105" s="30" t="s">
         <v>26</v>
@@ -6809,10 +6933,10 @@
     <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
       <c r="A106" s="13"/>
       <c r="B106" s="30" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C106" s="30" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D106" s="35" t="s">
         <v>26</v>
@@ -6830,10 +6954,10 @@
     <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
       <c r="A107" s="13"/>
       <c r="B107" s="30" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C107" s="30" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D107" s="35" t="s">
         <v>26</v>
@@ -6851,12 +6975,12 @@
     <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75">
       <c r="A108" s="13"/>
       <c r="B108" s="30" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C108" s="30" t="s">
-        <v>226</v>
-      </c>
-      <c r="D108" s="59" t="s">
+        <v>229</v>
+      </c>
+      <c r="D108" s="62" t="s">
         <v>26</v>
       </c>
       <c r="E108" s="31" t="s">
@@ -6872,10 +6996,10 @@
     <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
       <c r="A109" s="13"/>
       <c r="B109" s="30" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C109" s="30" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D109" s="35" t="s">
         <v>26</v>
@@ -6893,10 +7017,10 @@
     <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
       <c r="A110" s="13"/>
       <c r="B110" s="30" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C110" s="30" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D110" s="35" t="s">
         <v>26</v>
@@ -6914,10 +7038,10 @@
     <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
       <c r="A111" s="13"/>
       <c r="B111" s="30" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C111" s="30" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D111" s="35" t="s">
         <v>26</v>
@@ -6935,10 +7059,10 @@
     <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
       <c r="A112" s="13"/>
       <c r="B112" s="30" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C112" s="30" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D112" s="35" t="s">
         <v>26</v>
@@ -6956,10 +7080,10 @@
     <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
       <c r="A113" s="13"/>
       <c r="B113" s="30" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C113" s="30" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D113" s="35" t="s">
         <v>26</v>
@@ -6977,10 +7101,10 @@
     <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
       <c r="A114" s="13"/>
       <c r="B114" s="30" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C114" s="30" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D114" s="35" t="s">
         <v>26</v>
@@ -6996,53 +7120,53 @@
       <c r="K114" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
-      <c r="A115" s="52"/>
-      <c r="B115" s="45" t="s">
-        <v>239</v>
-      </c>
-      <c r="C115" s="60" t="s">
-        <v>240</v>
+      <c r="A115" s="55"/>
+      <c r="B115" s="48" t="s">
+        <v>242</v>
+      </c>
+      <c r="C115" s="63" t="s">
+        <v>243</v>
       </c>
       <c r="D115" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="E115" s="47" t="s">
+      <c r="E115" s="50" t="s">
         <v>27</v>
       </c>
       <c r="F115" s="4"/>
       <c r="G115" s="4"/>
-      <c r="H115" s="48"/>
-      <c r="I115" s="48"/>
+      <c r="H115" s="51"/>
+      <c r="I115" s="51"/>
       <c r="J115" s="11"/>
       <c r="K115" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
-      <c r="A116" s="52"/>
-      <c r="B116" s="45" t="s">
-        <v>241</v>
-      </c>
-      <c r="C116" s="60" t="s">
-        <v>242</v>
+      <c r="A116" s="55"/>
+      <c r="B116" s="48" t="s">
+        <v>244</v>
+      </c>
+      <c r="C116" s="63" t="s">
+        <v>245</v>
       </c>
       <c r="D116" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="E116" s="54" t="s">
+      <c r="E116" s="57" t="s">
         <v>27</v>
       </c>
       <c r="F116" s="4"/>
       <c r="G116" s="4"/>
-      <c r="H116" s="55"/>
-      <c r="I116" s="55"/>
+      <c r="H116" s="58"/>
+      <c r="I116" s="58"/>
       <c r="J116" s="11"/>
       <c r="K116" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75">
       <c r="A117" s="24" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B117" s="24" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C117" s="25"/>
       <c r="D117" s="26"/>
@@ -7059,10 +7183,10 @@
         <v>18</v>
       </c>
       <c r="B118" s="30" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C118" s="30" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D118" s="30" t="s">
         <v>26</v>
@@ -7080,10 +7204,10 @@
     <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18.75">
       <c r="A119" s="29"/>
       <c r="B119" s="30" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C119" s="30" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D119" s="35" t="s">
         <v>26</v>
@@ -7101,10 +7225,10 @@
     <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18.75">
       <c r="A120" s="29"/>
       <c r="B120" s="30" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C120" s="30" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D120" s="35" t="s">
         <v>26</v>
@@ -7122,10 +7246,10 @@
     <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="18.75">
       <c r="A121" s="29"/>
       <c r="B121" s="30" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C121" s="30" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D121" s="35" t="s">
         <v>26</v>
@@ -7143,10 +7267,10 @@
     <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="18.75">
       <c r="A122" s="29"/>
       <c r="B122" s="30" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C122" s="30" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D122" s="35" t="s">
         <v>26</v>
@@ -7163,25 +7287,25 @@
     </row>
     <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="18.75">
       <c r="A123" s="24" t="s">
-        <v>255</v>
-      </c>
-      <c r="B123" s="61"/>
-      <c r="C123" s="61"/>
-      <c r="D123" s="50"/>
-      <c r="E123" s="62"/>
+        <v>258</v>
+      </c>
+      <c r="B123" s="64"/>
+      <c r="C123" s="64"/>
+      <c r="D123" s="53"/>
+      <c r="E123" s="65"/>
       <c r="F123" s="4"/>
       <c r="G123" s="4"/>
-      <c r="H123" s="62"/>
-      <c r="I123" s="62"/>
+      <c r="H123" s="65"/>
+      <c r="I123" s="65"/>
       <c r="J123" s="11"/>
       <c r="K123" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="18.75">
       <c r="A124" s="29" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B124" s="30" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C124" s="30"/>
       <c r="D124" s="35" t="s">
@@ -7192,15 +7316,15 @@
       </c>
       <c r="F124" s="4"/>
       <c r="G124" s="4"/>
-      <c r="H124" s="44"/>
-      <c r="I124" s="44"/>
+      <c r="H124" s="47"/>
+      <c r="I124" s="47"/>
       <c r="J124" s="11"/>
       <c r="K124" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="18.75">
       <c r="A125" s="29"/>
       <c r="B125" s="30" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C125" s="30"/>
       <c r="D125" s="35" t="s">
@@ -7211,18 +7335,18 @@
       </c>
       <c r="F125" s="4"/>
       <c r="G125" s="4"/>
-      <c r="H125" s="44"/>
-      <c r="I125" s="44"/>
+      <c r="H125" s="47"/>
+      <c r="I125" s="47"/>
       <c r="J125" s="11"/>
       <c r="K125" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="18.75">
       <c r="A126" s="29"/>
       <c r="B126" s="30" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C126" s="30" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D126" s="35" t="s">
         <v>26</v>
@@ -7232,24 +7356,24 @@
       </c>
       <c r="F126" s="4"/>
       <c r="G126" s="4"/>
-      <c r="H126" s="44"/>
-      <c r="I126" s="44"/>
+      <c r="H126" s="47"/>
+      <c r="I126" s="47"/>
       <c r="J126" s="11"/>
       <c r="K126" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="18.75">
       <c r="A127" s="29"/>
       <c r="B127" s="30" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C127" s="30" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D127" s="35" t="s">
         <v>26</v>
       </c>
       <c r="E127" s="31" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F127" s="4"/>
       <c r="G127" s="4"/>
@@ -7261,16 +7385,16 @@
     <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="18.75">
       <c r="A128" s="29"/>
       <c r="B128" s="30" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C128" s="30" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D128" s="30" t="s">
         <v>26</v>
       </c>
       <c r="E128" s="31" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F128" s="4"/>
       <c r="G128" s="4"/>
@@ -7282,16 +7406,16 @@
     <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="18.75">
       <c r="A129" s="29"/>
       <c r="B129" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="C129" s="30" t="s">
+        <v>270</v>
+      </c>
+      <c r="D129" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="E129" s="31" t="s">
         <v>266</v>
-      </c>
-      <c r="C129" s="30" t="s">
-        <v>267</v>
-      </c>
-      <c r="D129" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="E129" s="31" t="s">
-        <v>263</v>
       </c>
       <c r="F129" s="4"/>
       <c r="G129" s="4"/>
@@ -7303,16 +7427,16 @@
     <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="18.75">
       <c r="A130" s="29"/>
       <c r="B130" s="30" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C130" s="30" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D130" s="35" t="s">
         <v>26</v>
       </c>
       <c r="E130" s="31" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F130" s="4"/>
       <c r="G130" s="4"/>
@@ -7324,16 +7448,16 @@
     <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="18.75">
       <c r="A131" s="29"/>
       <c r="B131" s="30" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C131" s="30" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D131" s="35" t="s">
         <v>26</v>
       </c>
       <c r="E131" s="31" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F131" s="4"/>
       <c r="G131" s="4"/>
@@ -7345,16 +7469,16 @@
     <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="18.75">
       <c r="A132" s="29"/>
       <c r="B132" s="30" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C132" s="30" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D132" s="35" t="s">
         <v>26</v>
       </c>
       <c r="E132" s="31" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F132" s="4"/>
       <c r="G132" s="4"/>
@@ -7366,16 +7490,16 @@
     <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75">
       <c r="A133" s="29"/>
       <c r="B133" s="30" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C133" s="30" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D133" s="43" t="s">
         <v>26</v>
       </c>
       <c r="E133" s="31" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F133" s="4"/>
       <c r="G133" s="4"/>
@@ -7387,27 +7511,27 @@
     <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="18.75">
       <c r="A134" s="29"/>
       <c r="B134" s="30" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C134" s="30" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D134" s="35" t="s">
         <v>26</v>
       </c>
       <c r="E134" s="41" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F134" s="4"/>
       <c r="G134" s="4"/>
-      <c r="H134" s="44"/>
-      <c r="I134" s="44"/>
+      <c r="H134" s="47"/>
+      <c r="I134" s="47"/>
       <c r="J134" s="11"/>
       <c r="K134" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="18.75">
       <c r="A135" s="29" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B135" s="30"/>
       <c r="C135" s="30"/>
@@ -7423,16 +7547,16 @@
     <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="18.75">
       <c r="A136" s="29"/>
       <c r="B136" s="30" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C136" s="30" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D136" s="35" t="s">
         <v>26</v>
       </c>
       <c r="E136" s="31" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F136" s="4"/>
       <c r="G136" s="4"/>
@@ -7444,16 +7568,16 @@
     <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="18.75">
       <c r="A137" s="29"/>
       <c r="B137" s="30" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C137" s="30" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D137" s="35" t="s">
         <v>26</v>
       </c>
       <c r="E137" s="31" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F137" s="4"/>
       <c r="G137" s="4"/>
@@ -7465,16 +7589,16 @@
     <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="18.75">
       <c r="A138" s="29"/>
       <c r="B138" s="30" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C138" s="30" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D138" s="35" t="s">
         <v>26</v>
       </c>
       <c r="E138" s="31" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F138" s="4"/>
       <c r="G138" s="4"/>
@@ -7486,16 +7610,16 @@
     <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="18.75">
       <c r="A139" s="29"/>
       <c r="B139" s="30" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C139" s="30" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D139" s="35" t="s">
         <v>26</v>
       </c>
       <c r="E139" s="31" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F139" s="4"/>
       <c r="G139" s="4"/>
@@ -7506,7 +7630,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A140" s="29" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B140" s="30"/>
       <c r="C140" s="30"/>
@@ -7522,10 +7646,10 @@
     <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="18.75">
       <c r="A141" s="29"/>
       <c r="B141" s="30" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C141" s="30" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D141" s="30" t="s">
         <v>26</v>
@@ -7543,10 +7667,10 @@
     <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="18.75">
       <c r="A142" s="29"/>
       <c r="B142" s="30" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C142" s="30" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D142" s="35" t="s">
         <v>26</v>
@@ -7564,10 +7688,10 @@
     <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="18.75">
       <c r="A143" s="29"/>
       <c r="B143" s="30" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C143" s="30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D143" s="35" t="s">
         <v>26</v>
@@ -7585,10 +7709,10 @@
     <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="18.75">
       <c r="A144" s="29"/>
       <c r="B144" s="30" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C144" s="30" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D144" s="35" t="s">
         <v>26</v>
@@ -7606,10 +7730,10 @@
     <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="18.75">
       <c r="A145" s="29"/>
       <c r="B145" s="30" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C145" s="30" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D145" s="35" t="s">
         <v>26</v>
@@ -7627,10 +7751,10 @@
     <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="18.75">
       <c r="A146" s="29"/>
       <c r="B146" s="30" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C146" s="30" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D146" s="35" t="s">
         <v>26</v>
@@ -7648,10 +7772,10 @@
     <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="18.75">
       <c r="A147" s="29"/>
       <c r="B147" s="30" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C147" s="30" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D147" s="35" t="s">
         <v>26</v>
@@ -7668,7 +7792,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="18.75">
       <c r="A148" s="29" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B148" s="30"/>
       <c r="C148" s="30"/>
@@ -7684,10 +7808,10 @@
     <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="18.75">
       <c r="A149" s="29"/>
       <c r="B149" s="30" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C149" s="30" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D149" s="35" t="s">
         <v>26</v>
@@ -7705,10 +7829,10 @@
     <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="18.75">
       <c r="A150" s="29"/>
       <c r="B150" s="30" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C150" s="30" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D150" s="35" t="s">
         <v>26</v>
@@ -7726,10 +7850,10 @@
     <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="18.75">
       <c r="A151" s="29"/>
       <c r="B151" s="30" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C151" s="30" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D151" s="43" t="s">
         <v>26</v>
@@ -7746,7 +7870,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A152" s="29" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B152" s="30"/>
       <c r="C152" s="30"/>
@@ -7762,10 +7886,10 @@
     <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="18.75">
       <c r="A153" s="29"/>
       <c r="B153" s="30" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C153" s="30" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="D153" s="30" t="s">
         <v>26</v>
@@ -7783,10 +7907,10 @@
     <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="18.75">
       <c r="A154" s="29"/>
       <c r="B154" s="30" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C154" s="30" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D154" s="35" t="s">
         <v>26</v>
@@ -7804,10 +7928,10 @@
     <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="18.75">
       <c r="A155" s="29"/>
       <c r="B155" s="30" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C155" s="30" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D155" s="35" t="s">
         <v>26</v>
@@ -7825,10 +7949,10 @@
     <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="18.75">
       <c r="A156" s="29"/>
       <c r="B156" s="30" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C156" s="30" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D156" s="35" t="s">
         <v>26</v>
@@ -7846,7 +7970,7 @@
     <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="18.75">
       <c r="A157" s="29"/>
       <c r="B157" s="30" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C157" s="30"/>
       <c r="D157" s="35" t="s">
@@ -7863,10 +7987,10 @@
     <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="18.75">
       <c r="A158" s="29"/>
       <c r="B158" s="30" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C158" s="30" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D158" s="35" t="s">
         <v>26</v>
@@ -7884,10 +8008,10 @@
     <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="18.75">
       <c r="A159" s="29"/>
       <c r="B159" s="30" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C159" s="30" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D159" s="35" t="s">
         <v>26</v>
@@ -7905,7 +8029,7 @@
     <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="18.75">
       <c r="A160" s="29"/>
       <c r="B160" s="30" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C160" s="30"/>
       <c r="D160" s="43" t="s">
@@ -7923,7 +8047,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A161" s="29" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B161" s="30"/>
       <c r="C161" s="30"/>
@@ -7939,7 +8063,7 @@
     <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="18.75">
       <c r="A162" s="29"/>
       <c r="B162" s="30" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C162" s="30"/>
       <c r="D162" s="35" t="s">
@@ -7958,10 +8082,10 @@
     <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="18.75">
       <c r="A163" s="29"/>
       <c r="B163" s="30" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C163" s="30" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D163" s="35" t="s">
         <v>26</v>
@@ -7979,10 +8103,10 @@
     <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="18.75">
       <c r="A164" s="29"/>
       <c r="B164" s="30" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C164" s="30" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D164" s="35" t="s">
         <v>26</v>
@@ -7999,11 +8123,11 @@
     </row>
     <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="18.75">
       <c r="A165" s="24" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B165" s="25"/>
       <c r="C165" s="25"/>
-      <c r="D165" s="50"/>
+      <c r="D165" s="53"/>
       <c r="E165" s="26"/>
       <c r="F165" s="4"/>
       <c r="G165" s="4"/>
@@ -8030,10 +8154,10 @@
     <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="18.75">
       <c r="A167" s="29"/>
       <c r="B167" s="30" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C167" s="30" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D167" s="30" t="s">
         <v>26</v>
@@ -8051,10 +8175,10 @@
     <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="18.75">
       <c r="A168" s="29"/>
       <c r="B168" s="30" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C168" s="30" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D168" s="35" t="s">
         <v>26</v>
@@ -8072,10 +8196,10 @@
     <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="18.75">
       <c r="A169" s="29"/>
       <c r="B169" s="30" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C169" s="30" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D169" s="35" t="s">
         <v>26</v>
@@ -8093,10 +8217,10 @@
     <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="18.75">
       <c r="A170" s="29"/>
       <c r="B170" s="30" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C170" s="30" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D170" s="43" t="s">
         <v>26</v>
@@ -8113,7 +8237,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="18.75">
       <c r="A171" s="29" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B171" s="30"/>
       <c r="C171" s="30"/>
@@ -8129,10 +8253,10 @@
     <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="18.75">
       <c r="A172" s="29"/>
       <c r="B172" s="30" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C172" s="30" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D172" s="35" t="s">
         <v>26</v>
@@ -8150,10 +8274,10 @@
     <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="18.75">
       <c r="A173" s="29"/>
       <c r="B173" s="30" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C173" s="30" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="D173" s="43" t="s">
         <v>26</v>
@@ -8170,7 +8294,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A174" s="29" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B174" s="30"/>
       <c r="C174" s="30"/>
@@ -8186,10 +8310,10 @@
     <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="18.75">
       <c r="A175" s="29"/>
       <c r="B175" s="30" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C175" s="30" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D175" s="35" t="s">
         <v>26</v>
@@ -8199,18 +8323,18 @@
       </c>
       <c r="F175" s="4"/>
       <c r="G175" s="4"/>
-      <c r="H175" s="44"/>
-      <c r="I175" s="44"/>
+      <c r="H175" s="47"/>
+      <c r="I175" s="47"/>
       <c r="J175" s="11"/>
       <c r="K175" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="18.75">
       <c r="A176" s="29"/>
       <c r="B176" s="30" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C176" s="30" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D176" s="35" t="s">
         <v>26</v>
@@ -8228,10 +8352,10 @@
     <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="18.75">
       <c r="A177" s="29"/>
       <c r="B177" s="43" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C177" s="30" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D177" s="35" t="s">
         <v>26</v>
@@ -8249,10 +8373,10 @@
     <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="18.75">
       <c r="A178" s="29"/>
       <c r="B178" s="30" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C178" s="30" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D178" s="35" t="s">
         <v>26</v>
@@ -8270,10 +8394,10 @@
     <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="18.75">
       <c r="A179" s="29"/>
       <c r="B179" s="30" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C179" s="30" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D179" s="30" t="s">
         <v>26</v>
@@ -8291,10 +8415,10 @@
     <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="18.75">
       <c r="A180" s="29"/>
       <c r="B180" s="30" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C180" s="30" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D180" s="35" t="s">
         <v>26</v>
@@ -8311,7 +8435,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A181" s="29" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B181" s="30"/>
       <c r="C181" s="30"/>
@@ -8327,10 +8451,10 @@
     <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="18.75">
       <c r="A182" s="29"/>
       <c r="B182" s="30" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C182" s="30" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="D182" s="35" t="s">
         <v>26</v>
@@ -8348,10 +8472,10 @@
     <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="18.75">
       <c r="A183" s="29"/>
       <c r="B183" s="30" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C183" s="30" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D183" s="35" t="s">
         <v>26</v>
@@ -8369,10 +8493,10 @@
     <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="18.75">
       <c r="A184" s="29"/>
       <c r="B184" s="30" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C184" s="30" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="D184" s="35" t="s">
         <v>26</v>
@@ -8390,10 +8514,10 @@
     <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="18.75">
       <c r="A185" s="29"/>
       <c r="B185" s="30" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C185" s="30" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D185" s="43" t="s">
         <v>26</v>
@@ -8410,7 +8534,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A186" s="29" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B186" s="30"/>
       <c r="C186" s="30"/>
@@ -8426,10 +8550,10 @@
     <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="18.75">
       <c r="A187" s="29"/>
       <c r="B187" s="30" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C187" s="30" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D187" s="35" t="s">
         <v>26</v>
@@ -8447,10 +8571,10 @@
     <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="18.75">
       <c r="A188" s="29"/>
       <c r="B188" s="30" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C188" s="30" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="D188" s="35" t="s">
         <v>26</v>
@@ -8468,10 +8592,10 @@
     <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="18.75">
       <c r="A189" s="29"/>
       <c r="B189" s="30" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C189" s="30" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D189" s="35" t="s">
         <v>26</v>
@@ -8488,7 +8612,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A190" s="29" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B190" s="30"/>
       <c r="C190" s="30"/>
@@ -8504,10 +8628,10 @@
     <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="18.75">
       <c r="A191" s="29"/>
       <c r="B191" s="30" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C191" s="30" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D191" s="30" t="s">
         <v>26</v>
@@ -8525,10 +8649,10 @@
     <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="18.75">
       <c r="A192" s="29"/>
       <c r="B192" s="30" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C192" s="30" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D192" s="35" t="s">
         <v>26</v>
@@ -8544,33 +8668,33 @@
       <c r="K192" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="18.75">
-      <c r="A193" s="52"/>
-      <c r="B193" s="63" t="s">
-        <v>377</v>
-      </c>
-      <c r="C193" s="64" t="s">
-        <v>378</v>
+      <c r="A193" s="55"/>
+      <c r="B193" s="66" t="s">
+        <v>380</v>
+      </c>
+      <c r="C193" s="67" t="s">
+        <v>381</v>
       </c>
       <c r="D193" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="E193" s="65" t="s">
+      <c r="E193" s="68" t="s">
         <v>27</v>
       </c>
       <c r="F193" s="4"/>
       <c r="G193" s="4"/>
-      <c r="H193" s="66"/>
-      <c r="I193" s="66"/>
+      <c r="H193" s="69"/>
+      <c r="I193" s="69"/>
       <c r="J193" s="11"/>
       <c r="K193" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="18.75">
       <c r="A194" s="24" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B194" s="25"/>
       <c r="C194" s="25"/>
-      <c r="D194" s="50"/>
+      <c r="D194" s="53"/>
       <c r="E194" s="26"/>
       <c r="F194" s="4"/>
       <c r="G194" s="4"/>
@@ -8581,7 +8705,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A195" s="29" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B195" s="30"/>
       <c r="C195" s="30"/>
@@ -8597,10 +8721,10 @@
     <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="18.75">
       <c r="A196" s="29"/>
       <c r="B196" s="30" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C196" s="30" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D196" s="35" t="s">
         <v>26</v>
@@ -8618,10 +8742,10 @@
     <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="18.75">
       <c r="A197" s="29"/>
       <c r="B197" s="30" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C197" s="30" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D197" s="43" t="s">
         <v>26</v>
@@ -8639,10 +8763,10 @@
     <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="18.75">
       <c r="A198" s="29"/>
       <c r="B198" s="30" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C198" s="30" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D198" s="35" t="s">
         <v>26</v>
@@ -8660,10 +8784,10 @@
     <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="18.75">
       <c r="A199" s="29"/>
       <c r="B199" s="30" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C199" s="30" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="D199" s="35" t="s">
         <v>26</v>
@@ -8681,10 +8805,10 @@
     <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="18.75">
       <c r="A200" s="29"/>
       <c r="B200" s="30" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C200" s="30" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D200" s="43" t="s">
         <v>26</v>
@@ -8701,26 +8825,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="18.75">
       <c r="A201" s="29" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B201" s="30"/>
       <c r="C201" s="30"/>
       <c r="D201" s="43"/>
-      <c r="E201" s="67"/>
+      <c r="E201" s="70"/>
       <c r="F201" s="4"/>
       <c r="G201" s="4"/>
-      <c r="H201" s="67"/>
-      <c r="I201" s="67"/>
+      <c r="H201" s="70"/>
+      <c r="I201" s="70"/>
       <c r="J201" s="11"/>
       <c r="K201" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="18.75">
       <c r="A202" s="29"/>
       <c r="B202" s="30" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C202" s="30" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D202" s="35" t="s">
         <v>26</v>
@@ -8738,10 +8862,10 @@
     <row x14ac:dyDescent="0.25" r="203" customHeight="1" ht="18.75">
       <c r="A203" s="29"/>
       <c r="B203" s="30" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C203" s="30" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D203" s="30" t="s">
         <v>26</v>
@@ -8759,10 +8883,10 @@
     <row x14ac:dyDescent="0.25" r="204" customHeight="1" ht="18.75">
       <c r="A204" s="29"/>
       <c r="B204" s="30" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C204" s="30" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D204" s="35" t="s">
         <v>26</v>
@@ -8780,10 +8904,10 @@
     <row x14ac:dyDescent="0.25" r="205" customHeight="1" ht="18.75">
       <c r="A205" s="29"/>
       <c r="B205" s="30" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C205" s="30" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D205" s="35" t="s">
         <v>26</v>
@@ -8801,10 +8925,10 @@
     <row x14ac:dyDescent="0.25" r="206" customHeight="1" ht="18.75">
       <c r="A206" s="29"/>
       <c r="B206" s="30" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C206" s="30" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D206" s="43" t="s">
         <v>26</v>
@@ -8820,37 +8944,37 @@
       <c r="K206" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="207" customHeight="1" ht="18.75">
-      <c r="A207" s="52"/>
-      <c r="B207" s="63" t="s">
-        <v>400</v>
-      </c>
-      <c r="C207" s="64" t="s">
-        <v>401</v>
+      <c r="A207" s="55"/>
+      <c r="B207" s="66" t="s">
+        <v>403</v>
+      </c>
+      <c r="C207" s="67" t="s">
+        <v>404</v>
       </c>
       <c r="D207" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="E207" s="65" t="s">
+      <c r="E207" s="68" t="s">
         <v>27</v>
       </c>
       <c r="F207" s="4"/>
       <c r="G207" s="4"/>
-      <c r="H207" s="66"/>
-      <c r="I207" s="66"/>
+      <c r="H207" s="69"/>
+      <c r="I207" s="69"/>
       <c r="J207" s="11"/>
       <c r="K207" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="208" customHeight="1" ht="18.75">
       <c r="A208" s="24" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B208" s="25" t="s">
-        <v>403</v>
-      </c>
-      <c r="C208" s="56" t="s">
-        <v>404</v>
-      </c>
-      <c r="D208" s="50"/>
+        <v>406</v>
+      </c>
+      <c r="C208" s="59" t="s">
+        <v>407</v>
+      </c>
+      <c r="D208" s="53"/>
       <c r="E208" s="26"/>
       <c r="F208" s="4"/>
       <c r="G208" s="4"/>
@@ -8861,7 +8985,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="209" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A209" s="29" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B209" s="30"/>
       <c r="C209" s="30"/>
@@ -8877,10 +9001,10 @@
     <row x14ac:dyDescent="0.25" r="210" customHeight="1" ht="18.75">
       <c r="A210" s="30"/>
       <c r="B210" s="30" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C210" s="30" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D210" s="35" t="s">
         <v>26</v>
@@ -8898,10 +9022,10 @@
     <row x14ac:dyDescent="0.25" r="211" customHeight="1" ht="18.75">
       <c r="A211" s="30"/>
       <c r="B211" s="30" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C211" s="30" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D211" s="35" t="s">
         <v>26</v>
@@ -8919,10 +9043,10 @@
     <row x14ac:dyDescent="0.25" r="212" customHeight="1" ht="18.75">
       <c r="A212" s="30"/>
       <c r="B212" s="30" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C212" s="30" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D212" s="35" t="s">
         <v>26</v>
@@ -8940,10 +9064,10 @@
     <row x14ac:dyDescent="0.25" r="213" customHeight="1" ht="18.75">
       <c r="A213" s="29"/>
       <c r="B213" s="30" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C213" s="30" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D213" s="35" t="s">
         <v>26</v>
@@ -8961,10 +9085,10 @@
     <row x14ac:dyDescent="0.25" r="214" customHeight="1" ht="18.75">
       <c r="A214" s="30"/>
       <c r="B214" s="30" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C214" s="30" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D214" s="35" t="s">
         <v>26</v>
@@ -8982,27 +9106,27 @@
     <row x14ac:dyDescent="0.25" r="215" customHeight="1" ht="18.75">
       <c r="A215" s="29"/>
       <c r="B215" s="30" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C215" s="30" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D215" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="E215" s="65" t="s">
+      <c r="E215" s="68" t="s">
         <v>27</v>
       </c>
       <c r="F215" s="4"/>
       <c r="G215" s="4"/>
-      <c r="H215" s="66"/>
-      <c r="I215" s="66"/>
+      <c r="H215" s="69"/>
+      <c r="I215" s="69"/>
       <c r="J215" s="11"/>
       <c r="K215" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="216" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A216" s="29" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B216" s="30"/>
       <c r="C216" s="30"/>
@@ -9018,10 +9142,10 @@
     <row x14ac:dyDescent="0.25" r="217" customHeight="1" ht="18.75">
       <c r="A217" s="30"/>
       <c r="B217" s="30" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C217" s="30" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D217" s="35" t="s">
         <v>26</v>
@@ -9039,10 +9163,10 @@
     <row x14ac:dyDescent="0.25" r="218" customHeight="1" ht="18.75">
       <c r="A218" s="29"/>
       <c r="B218" s="30" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C218" s="30" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D218" s="35" t="s">
         <v>26</v>
@@ -9060,10 +9184,10 @@
     <row x14ac:dyDescent="0.25" r="219" customHeight="1" ht="18.75">
       <c r="A219" s="29"/>
       <c r="B219" s="30" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C219" s="30" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D219" s="35" t="s">
         <v>26</v>
@@ -9081,10 +9205,10 @@
     <row x14ac:dyDescent="0.25" r="220" customHeight="1" ht="18.75">
       <c r="A220" s="29"/>
       <c r="B220" s="30" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C220" s="30" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D220" s="35" t="s">
         <v>26</v>
@@ -9102,10 +9226,10 @@
     <row x14ac:dyDescent="0.25" r="221" customHeight="1" ht="18.75">
       <c r="A221" s="29"/>
       <c r="B221" s="30" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C221" s="30" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="D221" s="35" t="s">
         <v>26</v>
@@ -9123,31 +9247,31 @@
     <row x14ac:dyDescent="0.25" r="222" customHeight="1" ht="18.75">
       <c r="A222" s="29"/>
       <c r="B222" s="30" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C222" s="30" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D222" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="E222" s="65" t="s">
+      <c r="E222" s="68" t="s">
         <v>27</v>
       </c>
       <c r="F222" s="4"/>
       <c r="G222" s="4"/>
-      <c r="H222" s="66"/>
-      <c r="I222" s="66"/>
+      <c r="H222" s="69"/>
+      <c r="I222" s="69"/>
       <c r="J222" s="11"/>
       <c r="K222" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="223" customHeight="1" ht="18.75">
       <c r="A223" s="29"/>
       <c r="B223" s="30" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C223" s="30" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="D223" s="35" t="s">
         <v>26</v>
@@ -9165,10 +9289,10 @@
     <row x14ac:dyDescent="0.25" r="224" customHeight="1" ht="18.75">
       <c r="A224" s="29"/>
       <c r="B224" s="30" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C224" s="30" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D224" s="35" t="s">
         <v>26</v>
@@ -9186,10 +9310,10 @@
     <row x14ac:dyDescent="0.25" r="225" customHeight="1" ht="18.75">
       <c r="A225" s="29"/>
       <c r="B225" s="30" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C225" s="30" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D225" s="35" t="s">
         <v>26</v>
@@ -9207,10 +9331,10 @@
     <row x14ac:dyDescent="0.25" r="226" customHeight="1" ht="18.75">
       <c r="A226" s="29"/>
       <c r="B226" s="30" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C226" s="30" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D226" s="35" t="s">
         <v>26</v>
@@ -9228,10 +9352,10 @@
     <row x14ac:dyDescent="0.25" r="227" customHeight="1" ht="18.75">
       <c r="A227" s="29"/>
       <c r="B227" s="30" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C227" s="30" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="D227" s="30" t="s">
         <v>26</v>
@@ -9249,10 +9373,10 @@
     <row x14ac:dyDescent="0.25" r="228" customHeight="1" ht="18.75">
       <c r="A228" s="29"/>
       <c r="B228" s="30" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C228" s="30" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D228" s="35" t="s">
         <v>26</v>
@@ -9270,10 +9394,10 @@
     <row x14ac:dyDescent="0.25" r="229" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A229" s="29"/>
       <c r="B229" s="30" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C229" s="30" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="D229" s="35" t="s">
         <v>26</v>
@@ -9289,10 +9413,10 @@
     <row x14ac:dyDescent="0.25" r="230" customHeight="1" ht="18.75">
       <c r="A230" s="29"/>
       <c r="B230" s="30" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C230" s="30" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="D230" s="35" t="s">
         <v>26</v>
@@ -9310,10 +9434,10 @@
     <row x14ac:dyDescent="0.25" r="231" customHeight="1" ht="18.75">
       <c r="A231" s="29"/>
       <c r="B231" s="30" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C231" s="30" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D231" s="35" t="s">
         <v>26</v>
@@ -9331,45 +9455,45 @@
     <row x14ac:dyDescent="0.25" r="232" customHeight="1" ht="18.75">
       <c r="A232" s="29"/>
       <c r="B232" s="30" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C232" s="30" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D232" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="E232" s="67" t="s">
+      <c r="E232" s="70" t="s">
         <v>27</v>
       </c>
       <c r="F232" s="4"/>
       <c r="G232" s="4"/>
-      <c r="H232" s="67"/>
-      <c r="I232" s="67"/>
+      <c r="H232" s="70"/>
+      <c r="I232" s="70"/>
       <c r="J232" s="11"/>
       <c r="K232" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="233" customHeight="1" ht="18.75">
       <c r="A233" s="24" t="s">
-        <v>451</v>
-      </c>
-      <c r="B233" s="61"/>
-      <c r="C233" s="61"/>
-      <c r="D233" s="50"/>
-      <c r="E233" s="62"/>
+        <v>454</v>
+      </c>
+      <c r="B233" s="64"/>
+      <c r="C233" s="64"/>
+      <c r="D233" s="53"/>
+      <c r="E233" s="65"/>
       <c r="F233" s="4"/>
       <c r="G233" s="4"/>
-      <c r="H233" s="62"/>
-      <c r="I233" s="62"/>
+      <c r="H233" s="65"/>
+      <c r="I233" s="65"/>
       <c r="J233" s="11"/>
       <c r="K233" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="234" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A234" s="29" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B234" s="30" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C234" s="30"/>
       <c r="D234" s="35" t="s">
@@ -9386,10 +9510,10 @@
     <row x14ac:dyDescent="0.25" r="235" customHeight="1" ht="18.75">
       <c r="A235" s="29"/>
       <c r="B235" s="30" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C235" s="30" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D235" s="35" t="s">
         <v>26</v>
@@ -9407,10 +9531,10 @@
     <row x14ac:dyDescent="0.25" r="236" customHeight="1" ht="18.75">
       <c r="A236" s="29"/>
       <c r="B236" s="30" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C236" s="30" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D236" s="35" t="s">
         <v>26</v>
@@ -9428,10 +9552,10 @@
     <row x14ac:dyDescent="0.25" r="237" customHeight="1" ht="18.75">
       <c r="A237" s="29"/>
       <c r="B237" s="30" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C237" s="30" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D237" s="35" t="s">
         <v>26</v>
@@ -9449,10 +9573,10 @@
     <row x14ac:dyDescent="0.25" r="238" customHeight="1" ht="18.75">
       <c r="A238" s="29"/>
       <c r="B238" s="30" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C238" s="30" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="D238" s="35" t="s">
         <v>26</v>
@@ -9470,10 +9594,10 @@
     <row x14ac:dyDescent="0.25" r="239" customHeight="1" ht="18.75">
       <c r="A239" s="29"/>
       <c r="B239" s="43" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C239" s="30" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="D239" s="30" t="s">
         <v>26</v>
@@ -9491,10 +9615,10 @@
     <row x14ac:dyDescent="0.25" r="240" customHeight="1" ht="18.75">
       <c r="A240" s="29"/>
       <c r="B240" s="43" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C240" s="30" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D240" s="35" t="s">
         <v>26</v>
@@ -9512,10 +9636,10 @@
     <row x14ac:dyDescent="0.25" r="241" customHeight="1" ht="18.75">
       <c r="A241" s="29"/>
       <c r="B241" s="30" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C241" s="30" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="D241" s="35" t="s">
         <v>26</v>
@@ -9533,10 +9657,10 @@
     <row x14ac:dyDescent="0.25" r="242" customHeight="1" ht="18.75">
       <c r="A242" s="29"/>
       <c r="B242" s="30" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C242" s="30" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="D242" s="35" t="s">
         <v>26</v>
@@ -9554,31 +9678,31 @@
     <row x14ac:dyDescent="0.25" r="243" customHeight="1" ht="18.75">
       <c r="A243" s="29"/>
       <c r="B243" s="30" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C243" s="30" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D243" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="E243" s="65" t="s">
+      <c r="E243" s="68" t="s">
         <v>27</v>
       </c>
       <c r="F243" s="4"/>
       <c r="G243" s="4"/>
-      <c r="H243" s="66"/>
-      <c r="I243" s="66"/>
+      <c r="H243" s="69"/>
+      <c r="I243" s="69"/>
       <c r="J243" s="11"/>
       <c r="K243" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="244" customHeight="1" ht="18.75">
       <c r="A244" s="29"/>
       <c r="B244" s="30" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C244" s="30" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D244" s="35" t="s">
         <v>26</v>
@@ -9596,10 +9720,10 @@
     <row x14ac:dyDescent="0.25" r="245" customHeight="1" ht="18.75">
       <c r="A245" s="29"/>
       <c r="B245" s="30" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C245" s="30" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D245" s="43" t="s">
         <v>26</v>
@@ -9616,23 +9740,23 @@
     </row>
     <row x14ac:dyDescent="0.25" r="246" customHeight="1" ht="18.75">
       <c r="A246" s="29" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B246" s="30"/>
       <c r="C246" s="30"/>
       <c r="D246" s="43"/>
-      <c r="E246" s="67"/>
+      <c r="E246" s="70"/>
       <c r="F246" s="4"/>
       <c r="G246" s="4"/>
-      <c r="H246" s="67"/>
-      <c r="I246" s="67"/>
+      <c r="H246" s="70"/>
+      <c r="I246" s="70"/>
       <c r="J246" s="11"/>
       <c r="K246" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="247" customHeight="1" ht="18.75">
       <c r="A247" s="29"/>
       <c r="B247" s="30" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C247" s="30"/>
       <c r="D247" s="43" t="s">
@@ -9651,10 +9775,10 @@
     <row x14ac:dyDescent="0.25" r="248" customHeight="1" ht="18.75">
       <c r="A248" s="29"/>
       <c r="B248" s="30" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C248" s="30" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="D248" s="35" t="s">
         <v>26</v>
@@ -9672,10 +9796,10 @@
     <row x14ac:dyDescent="0.25" r="249" customHeight="1" ht="18.75">
       <c r="A249" s="29"/>
       <c r="B249" s="30" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C249" s="30" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D249" s="35" t="s">
         <v>26</v>
@@ -9693,10 +9817,10 @@
     <row x14ac:dyDescent="0.25" r="250" customHeight="1" ht="18.75">
       <c r="A250" s="29"/>
       <c r="B250" s="30" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C250" s="30" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="D250" s="35" t="s">
         <v>26</v>
@@ -9714,10 +9838,10 @@
     <row x14ac:dyDescent="0.25" r="251" customHeight="1" ht="18.75">
       <c r="A251" s="29"/>
       <c r="B251" s="30" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C251" s="30" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D251" s="35" t="s">
         <v>26</v>
@@ -9735,10 +9859,10 @@
     <row x14ac:dyDescent="0.25" r="252" customHeight="1" ht="18.75">
       <c r="A252" s="29"/>
       <c r="B252" s="30" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C252" s="30" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="D252" s="30" t="s">
         <v>26</v>
@@ -9756,10 +9880,10 @@
     <row x14ac:dyDescent="0.25" r="253" customHeight="1" ht="18.75">
       <c r="A253" s="29"/>
       <c r="B253" s="30" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C253" s="30" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D253" s="35" t="s">
         <v>26</v>
@@ -9777,10 +9901,10 @@
     <row x14ac:dyDescent="0.25" r="254" customHeight="1" ht="18.75">
       <c r="A254" s="29"/>
       <c r="B254" s="30" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C254" s="30" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="D254" s="43" t="s">
         <v>26</v>
@@ -9798,10 +9922,10 @@
     <row x14ac:dyDescent="0.25" r="255" customHeight="1" ht="18.75">
       <c r="A255" s="29"/>
       <c r="B255" s="30" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C255" s="30" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D255" s="35" t="s">
         <v>26</v>
@@ -9819,10 +9943,10 @@
     <row x14ac:dyDescent="0.25" r="256" customHeight="1" ht="18.75">
       <c r="A256" s="29"/>
       <c r="B256" s="30" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C256" s="30" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="D256" s="35" t="s">
         <v>26</v>
@@ -9840,10 +9964,10 @@
     <row x14ac:dyDescent="0.25" r="257" customHeight="1" ht="22.5">
       <c r="A257" s="29"/>
       <c r="B257" s="30" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C257" s="30" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="D257" s="35" t="s">
         <v>26</v>
@@ -9860,7 +9984,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="258" customHeight="1" ht="22.5">
       <c r="A258" s="29" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B258" s="30"/>
       <c r="C258" s="30"/>
@@ -9876,10 +10000,10 @@
     <row x14ac:dyDescent="0.25" r="259" customHeight="1" ht="18.75">
       <c r="A259" s="29"/>
       <c r="B259" s="30" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C259" s="30" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="D259" s="35" t="s">
         <v>26</v>
@@ -9897,10 +10021,10 @@
     <row x14ac:dyDescent="0.25" r="260" customHeight="1" ht="18.75">
       <c r="A260" s="29"/>
       <c r="B260" s="30" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C260" s="30" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="D260" s="43" t="s">
         <v>26</v>
@@ -9918,10 +10042,10 @@
     <row x14ac:dyDescent="0.25" r="261" customHeight="1" ht="18.75">
       <c r="A261" s="29"/>
       <c r="B261" s="30" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C261" s="30" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="D261" s="43" t="s">
         <v>26</v>
@@ -9939,10 +10063,10 @@
     <row x14ac:dyDescent="0.25" r="262" customHeight="1" ht="18.75">
       <c r="A262" s="29"/>
       <c r="B262" s="30" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C262" s="30" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="D262" s="35" t="s">
         <v>26</v>
@@ -9960,10 +10084,10 @@
     <row x14ac:dyDescent="0.25" r="263" customHeight="1" ht="18.75">
       <c r="A263" s="29"/>
       <c r="B263" s="30" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C263" s="30" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D263" s="35" t="s">
         <v>26</v>
@@ -9981,7 +10105,7 @@
     <row x14ac:dyDescent="0.25" r="264" customHeight="1" ht="18.75">
       <c r="A264" s="29"/>
       <c r="B264" s="30" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C264" s="30"/>
       <c r="D264" s="35" t="s">
@@ -10000,10 +10124,10 @@
     <row x14ac:dyDescent="0.25" r="265" customHeight="1" ht="18.75">
       <c r="A265" s="29"/>
       <c r="B265" s="30" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C265" s="30" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D265" s="30" t="s">
         <v>26</v>
@@ -10021,10 +10145,10 @@
     <row x14ac:dyDescent="0.25" r="266" customHeight="1" ht="18.75">
       <c r="A266" s="29"/>
       <c r="B266" s="30" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C266" s="30" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D266" s="35" t="s">
         <v>26</v>
@@ -10042,10 +10166,10 @@
     <row x14ac:dyDescent="0.25" r="267" customHeight="1" ht="18.75">
       <c r="A267" s="29"/>
       <c r="B267" s="30" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C267" s="30" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="D267" s="35" t="s">
         <v>26</v>
@@ -10062,10 +10186,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="268" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A268" s="29" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B268" s="30" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C268" s="30"/>
       <c r="D268" s="35" t="s">
@@ -10082,10 +10206,10 @@
     <row x14ac:dyDescent="0.25" r="269" customHeight="1" ht="18.75">
       <c r="A269" s="29"/>
       <c r="B269" s="30" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C269" s="30" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D269" s="35" t="s">
         <v>26</v>
@@ -10103,10 +10227,10 @@
     <row x14ac:dyDescent="0.25" r="270" customHeight="1" ht="18.75">
       <c r="A270" s="29"/>
       <c r="B270" s="30" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C270" s="30" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D270" s="35" t="s">
         <v>26</v>
@@ -10124,10 +10248,10 @@
     <row x14ac:dyDescent="0.25" r="271" customHeight="1" ht="18.75">
       <c r="A271" s="29"/>
       <c r="B271" s="30" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C271" s="30" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D271" s="43" t="s">
         <v>26</v>
@@ -10145,10 +10269,10 @@
     <row x14ac:dyDescent="0.25" r="272" customHeight="1" ht="18.75">
       <c r="A272" s="29"/>
       <c r="B272" s="30" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C272" s="30" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="D272" s="35" t="s">
         <v>26</v>
@@ -10166,10 +10290,10 @@
     <row x14ac:dyDescent="0.25" r="273" customHeight="1" ht="18.75">
       <c r="A273" s="29"/>
       <c r="B273" s="30" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C273" s="30" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D273" s="35" t="s">
         <v>26</v>
@@ -10187,10 +10311,10 @@
     <row x14ac:dyDescent="0.25" r="274" customHeight="1" ht="18.75">
       <c r="A274" s="29"/>
       <c r="B274" s="30" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C274" s="30" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="D274" s="43" t="s">
         <v>26</v>
@@ -10208,10 +10332,10 @@
     <row x14ac:dyDescent="0.25" r="275" customHeight="1" ht="18.75">
       <c r="A275" s="29"/>
       <c r="B275" s="30" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C275" s="30" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D275" s="35" t="s">
         <v>26</v>
@@ -10229,10 +10353,10 @@
     <row x14ac:dyDescent="0.25" r="276" customHeight="1" ht="18.75">
       <c r="A276" s="29"/>
       <c r="B276" s="30" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C276" s="30" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D276" s="35" t="s">
         <v>26</v>
@@ -10250,10 +10374,10 @@
     <row x14ac:dyDescent="0.25" r="277" customHeight="1" ht="18.75">
       <c r="A277" s="29"/>
       <c r="B277" s="30" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="C277" s="30" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D277" s="30" t="s">
         <v>26</v>
@@ -10271,10 +10395,10 @@
     <row x14ac:dyDescent="0.25" r="278" customHeight="1" ht="18.75">
       <c r="A278" s="29"/>
       <c r="B278" s="30" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C278" s="30" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="D278" s="35" t="s">
         <v>26</v>
@@ -10292,10 +10416,10 @@
     <row x14ac:dyDescent="0.25" r="279" customHeight="1" ht="18.75">
       <c r="A279" s="29"/>
       <c r="B279" s="30" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="C279" s="30" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="D279" s="35" t="s">
         <v>26</v>
@@ -10313,16 +10437,16 @@
     <row x14ac:dyDescent="0.25" r="280" customHeight="1" ht="18.75">
       <c r="A280" s="29"/>
       <c r="B280" s="30" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C280" s="30" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D280" s="43" t="s">
         <v>26</v>
       </c>
       <c r="E280" s="31" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="F280" s="4"/>
       <c r="G280" s="4"/>
@@ -10334,10 +10458,10 @@
     <row x14ac:dyDescent="0.25" r="281" customHeight="1" ht="18.75">
       <c r="A281" s="29"/>
       <c r="B281" s="30" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C281" s="30" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D281" s="35" t="s">
         <v>26</v>
@@ -10355,10 +10479,10 @@
     <row x14ac:dyDescent="0.25" r="282" customHeight="1" ht="18.75">
       <c r="A282" s="29"/>
       <c r="B282" s="30" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C282" s="30" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="D282" s="35" t="s">
         <v>26</v>
@@ -10375,7 +10499,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="283" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A283" s="29" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B283" s="30"/>
       <c r="C283" s="30"/>
@@ -10391,10 +10515,10 @@
     <row x14ac:dyDescent="0.25" r="284" customHeight="1" ht="18.75">
       <c r="A284" s="29"/>
       <c r="B284" s="30" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C284" s="30" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D284" s="35" t="s">
         <v>26</v>
@@ -10411,11 +10535,11 @@
     </row>
     <row x14ac:dyDescent="0.25" r="285" customHeight="1" ht="18.75">
       <c r="A285" s="29"/>
-      <c r="B285" s="52" t="s">
-        <v>549</v>
+      <c r="B285" s="55" t="s">
+        <v>552</v>
       </c>
       <c r="C285" s="30" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D285" s="35" t="s">
         <v>26</v>
@@ -10433,10 +10557,10 @@
     <row x14ac:dyDescent="0.25" r="286" customHeight="1" ht="18.75">
       <c r="A286" s="29"/>
       <c r="B286" s="30" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C286" s="30" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D286" s="35" t="s">
         <v>26</v>
@@ -10454,10 +10578,10 @@
     <row x14ac:dyDescent="0.25" r="287" customHeight="1" ht="18.75">
       <c r="A287" s="29"/>
       <c r="B287" s="30" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C287" s="30" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="D287" s="43" t="s">
         <v>26</v>
@@ -10474,7 +10598,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="288" customHeight="1" ht="18.75">
       <c r="A288" s="29" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B288" s="30"/>
       <c r="C288" s="30"/>
@@ -10490,10 +10614,10 @@
     <row x14ac:dyDescent="0.25" r="289" customHeight="1" ht="18.75">
       <c r="A289" s="29"/>
       <c r="B289" s="30" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C289" s="30" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="D289" s="30" t="s">
         <v>26</v>
@@ -10511,10 +10635,10 @@
     <row x14ac:dyDescent="0.25" r="290" customHeight="1" ht="18.75">
       <c r="A290" s="29"/>
       <c r="B290" s="30" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C290" s="30" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="D290" s="43" t="s">
         <v>26</v>
@@ -10532,10 +10656,10 @@
     <row x14ac:dyDescent="0.25" r="291" customHeight="1" ht="18.75">
       <c r="A291" s="29"/>
       <c r="B291" s="30" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C291" s="30" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="D291" s="35" t="s">
         <v>26</v>
@@ -10553,10 +10677,10 @@
     <row x14ac:dyDescent="0.25" r="292" customHeight="1" ht="18.75">
       <c r="A292" s="29"/>
       <c r="B292" s="30" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C292" s="30" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="D292" s="35" t="s">
         <v>26</v>
@@ -10574,10 +10698,10 @@
     <row x14ac:dyDescent="0.25" r="293" customHeight="1" ht="18.75">
       <c r="A293" s="29"/>
       <c r="B293" s="30" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C293" s="30" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D293" s="35" t="s">
         <v>26</v>
@@ -10594,47 +10718,47 @@
     </row>
     <row x14ac:dyDescent="0.25" r="294" customHeight="1" ht="18.75">
       <c r="A294" s="24" t="s">
-        <v>566</v>
-      </c>
-      <c r="B294" s="68" t="s">
-        <v>567</v>
-      </c>
-      <c r="C294" s="69" t="s">
-        <v>568</v>
-      </c>
-      <c r="D294" s="50"/>
-      <c r="E294" s="70"/>
+        <v>569</v>
+      </c>
+      <c r="B294" s="71" t="s">
+        <v>570</v>
+      </c>
+      <c r="C294" s="72" t="s">
+        <v>571</v>
+      </c>
+      <c r="D294" s="53"/>
+      <c r="E294" s="73"/>
       <c r="F294" s="4"/>
       <c r="G294" s="4"/>
-      <c r="H294" s="70"/>
-      <c r="I294" s="70"/>
+      <c r="H294" s="73"/>
+      <c r="I294" s="73"/>
       <c r="J294" s="11"/>
       <c r="K294" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="295" customHeight="1" ht="18.75">
-      <c r="A295" s="71" t="s">
-        <v>569</v>
-      </c>
-      <c r="B295" s="71" t="s">
-        <v>570</v>
-      </c>
-      <c r="C295" s="63"/>
+      <c r="A295" s="74" t="s">
+        <v>572</v>
+      </c>
+      <c r="B295" s="74" t="s">
+        <v>573</v>
+      </c>
+      <c r="C295" s="66"/>
       <c r="D295" s="43"/>
-      <c r="E295" s="72"/>
+      <c r="E295" s="75"/>
       <c r="F295" s="4"/>
       <c r="G295" s="4"/>
-      <c r="H295" s="72"/>
-      <c r="I295" s="72"/>
+      <c r="H295" s="75"/>
+      <c r="I295" s="75"/>
       <c r="J295" s="11"/>
       <c r="K295" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="296" customHeight="1" ht="18.75">
-      <c r="A296" s="71"/>
-      <c r="B296" s="45" t="s">
-        <v>571</v>
-      </c>
-      <c r="C296" s="46" t="s">
-        <v>572</v>
+      <c r="A296" s="74"/>
+      <c r="B296" s="48" t="s">
+        <v>574</v>
+      </c>
+      <c r="C296" s="49" t="s">
+        <v>575</v>
       </c>
       <c r="D296" s="35" t="s">
         <v>26</v>
@@ -10650,12 +10774,12 @@
       <c r="K296" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="297" customHeight="1" ht="18.75">
-      <c r="A297" s="71"/>
-      <c r="B297" s="45" t="s">
-        <v>573</v>
-      </c>
-      <c r="C297" s="46" t="s">
-        <v>574</v>
+      <c r="A297" s="74"/>
+      <c r="B297" s="48" t="s">
+        <v>576</v>
+      </c>
+      <c r="C297" s="49" t="s">
+        <v>577</v>
       </c>
       <c r="D297" s="35" t="s">
         <v>26</v>
@@ -10671,12 +10795,12 @@
       <c r="K297" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="298" customHeight="1" ht="18.75">
-      <c r="A298" s="71"/>
-      <c r="B298" s="45" t="s">
-        <v>575</v>
-      </c>
-      <c r="C298" s="46" t="s">
-        <v>576</v>
+      <c r="A298" s="74"/>
+      <c r="B298" s="48" t="s">
+        <v>578</v>
+      </c>
+      <c r="C298" s="49" t="s">
+        <v>579</v>
       </c>
       <c r="D298" s="35" t="s">
         <v>26</v>
@@ -10692,12 +10816,12 @@
       <c r="K298" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="299" customHeight="1" ht="18.75">
-      <c r="A299" s="71"/>
-      <c r="B299" s="45" t="s">
-        <v>577</v>
-      </c>
-      <c r="C299" s="46" t="s">
-        <v>578</v>
+      <c r="A299" s="74"/>
+      <c r="B299" s="48" t="s">
+        <v>580</v>
+      </c>
+      <c r="C299" s="49" t="s">
+        <v>581</v>
       </c>
       <c r="D299" s="35" t="s">
         <v>26</v>
@@ -10713,12 +10837,12 @@
       <c r="K299" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="300" customHeight="1" ht="18.75">
-      <c r="A300" s="71"/>
-      <c r="B300" s="45" t="s">
-        <v>579</v>
-      </c>
-      <c r="C300" s="46" t="s">
-        <v>580</v>
+      <c r="A300" s="74"/>
+      <c r="B300" s="48" t="s">
+        <v>582</v>
+      </c>
+      <c r="C300" s="49" t="s">
+        <v>583</v>
       </c>
       <c r="D300" s="43" t="s">
         <v>26</v>
@@ -10734,12 +10858,12 @@
       <c r="K300" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="301" customHeight="1" ht="18.75">
-      <c r="A301" s="71"/>
-      <c r="B301" s="45" t="s">
-        <v>581</v>
-      </c>
-      <c r="C301" s="46" t="s">
-        <v>582</v>
+      <c r="A301" s="74"/>
+      <c r="B301" s="48" t="s">
+        <v>584</v>
+      </c>
+      <c r="C301" s="49" t="s">
+        <v>585</v>
       </c>
       <c r="D301" s="35" t="s">
         <v>26</v>
@@ -10755,12 +10879,12 @@
       <c r="K301" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="302" customHeight="1" ht="18.75">
-      <c r="A302" s="71"/>
-      <c r="B302" s="45" t="s">
-        <v>583</v>
-      </c>
-      <c r="C302" s="46" t="s">
-        <v>584</v>
+      <c r="A302" s="74"/>
+      <c r="B302" s="48" t="s">
+        <v>586</v>
+      </c>
+      <c r="C302" s="49" t="s">
+        <v>587</v>
       </c>
       <c r="D302" s="35" t="s">
         <v>26</v>
@@ -10776,12 +10900,12 @@
       <c r="K302" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="303" customHeight="1" ht="18.75">
-      <c r="A303" s="71"/>
-      <c r="B303" s="45" t="s">
-        <v>585</v>
-      </c>
-      <c r="C303" s="46" t="s">
-        <v>586</v>
+      <c r="A303" s="74"/>
+      <c r="B303" s="48" t="s">
+        <v>588</v>
+      </c>
+      <c r="C303" s="49" t="s">
+        <v>589</v>
       </c>
       <c r="D303" s="35" t="s">
         <v>26</v>
@@ -10797,12 +10921,12 @@
       <c r="K303" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="304" customHeight="1" ht="18.75">
-      <c r="A304" s="71"/>
-      <c r="B304" s="45" t="s">
-        <v>587</v>
-      </c>
-      <c r="C304" s="46" t="s">
-        <v>588</v>
+      <c r="A304" s="74"/>
+      <c r="B304" s="48" t="s">
+        <v>590</v>
+      </c>
+      <c r="C304" s="49" t="s">
+        <v>591</v>
       </c>
       <c r="D304" s="30" t="s">
         <v>26</v>
@@ -10818,12 +10942,12 @@
       <c r="K304" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="305" customHeight="1" ht="18.75">
-      <c r="A305" s="71"/>
-      <c r="B305" s="45" t="s">
-        <v>589</v>
-      </c>
-      <c r="C305" s="46" t="s">
-        <v>590</v>
+      <c r="A305" s="74"/>
+      <c r="B305" s="48" t="s">
+        <v>592</v>
+      </c>
+      <c r="C305" s="49" t="s">
+        <v>593</v>
       </c>
       <c r="D305" s="35" t="s">
         <v>26</v>
@@ -10839,12 +10963,12 @@
       <c r="K305" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="306" customHeight="1" ht="18.75">
-      <c r="A306" s="71"/>
-      <c r="B306" s="45" t="s">
-        <v>591</v>
-      </c>
-      <c r="C306" s="46" t="s">
-        <v>592</v>
+      <c r="A306" s="74"/>
+      <c r="B306" s="48" t="s">
+        <v>594</v>
+      </c>
+      <c r="C306" s="49" t="s">
+        <v>595</v>
       </c>
       <c r="D306" s="43"/>
       <c r="E306" s="32"/>
@@ -10856,12 +10980,12 @@
       <c r="K306" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="307" customHeight="1" ht="18.75">
-      <c r="A307" s="71"/>
-      <c r="B307" s="45" t="s">
-        <v>593</v>
-      </c>
-      <c r="C307" s="46" t="s">
-        <v>594</v>
+      <c r="A307" s="74"/>
+      <c r="B307" s="48" t="s">
+        <v>596</v>
+      </c>
+      <c r="C307" s="49" t="s">
+        <v>597</v>
       </c>
       <c r="D307" s="35" t="s">
         <v>26</v>
@@ -10877,12 +11001,12 @@
       <c r="K307" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="308" customHeight="1" ht="18.75">
-      <c r="A308" s="71"/>
-      <c r="B308" s="45" t="s">
-        <v>595</v>
-      </c>
-      <c r="C308" s="46" t="s">
-        <v>596</v>
+      <c r="A308" s="74"/>
+      <c r="B308" s="48" t="s">
+        <v>598</v>
+      </c>
+      <c r="C308" s="49" t="s">
+        <v>599</v>
       </c>
       <c r="D308" s="35" t="s">
         <v>26</v>
@@ -10898,12 +11022,12 @@
       <c r="K308" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="309" customHeight="1" ht="18.75">
-      <c r="A309" s="71"/>
-      <c r="B309" s="45" t="s">
-        <v>597</v>
-      </c>
-      <c r="C309" s="46" t="s">
-        <v>598</v>
+      <c r="A309" s="74"/>
+      <c r="B309" s="48" t="s">
+        <v>600</v>
+      </c>
+      <c r="C309" s="49" t="s">
+        <v>601</v>
       </c>
       <c r="D309" s="35" t="s">
         <v>26</v>
@@ -10919,12 +11043,12 @@
       <c r="K309" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="310" customHeight="1" ht="18.75">
-      <c r="A310" s="71"/>
-      <c r="B310" s="45" t="s">
-        <v>599</v>
-      </c>
-      <c r="C310" s="46" t="s">
-        <v>600</v>
+      <c r="A310" s="74"/>
+      <c r="B310" s="48" t="s">
+        <v>602</v>
+      </c>
+      <c r="C310" s="49" t="s">
+        <v>603</v>
       </c>
       <c r="D310" s="35" t="s">
         <v>26</v>
@@ -10940,12 +11064,12 @@
       <c r="K310" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="311" customHeight="1" ht="18.75">
-      <c r="A311" s="71"/>
-      <c r="B311" s="45" t="s">
-        <v>601</v>
-      </c>
-      <c r="C311" s="46" t="s">
-        <v>602</v>
+      <c r="A311" s="74"/>
+      <c r="B311" s="48" t="s">
+        <v>604</v>
+      </c>
+      <c r="C311" s="49" t="s">
+        <v>605</v>
       </c>
       <c r="D311" s="35" t="s">
         <v>26</v>
@@ -10963,10 +11087,10 @@
     <row x14ac:dyDescent="0.25" r="312" customHeight="1" ht="18.75">
       <c r="A312" s="29"/>
       <c r="B312" s="30" t="s">
-        <v>603</v>
-      </c>
-      <c r="C312" s="73" t="s">
-        <v>604</v>
+        <v>606</v>
+      </c>
+      <c r="C312" s="76" t="s">
+        <v>607</v>
       </c>
       <c r="D312" s="35" t="s">
         <v>26</v>
@@ -10982,12 +11106,12 @@
       <c r="K312" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="313" customHeight="1" ht="18.75">
-      <c r="A313" s="71"/>
-      <c r="B313" s="45" t="s">
-        <v>605</v>
-      </c>
-      <c r="C313" s="46" t="s">
-        <v>606</v>
+      <c r="A313" s="74"/>
+      <c r="B313" s="48" t="s">
+        <v>608</v>
+      </c>
+      <c r="C313" s="49" t="s">
+        <v>609</v>
       </c>
       <c r="D313" s="35" t="s">
         <v>26</v>
@@ -11003,12 +11127,12 @@
       <c r="K313" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="314" customHeight="1" ht="18.75">
-      <c r="A314" s="71"/>
-      <c r="B314" s="45" t="s">
-        <v>607</v>
-      </c>
-      <c r="C314" s="46" t="s">
-        <v>608</v>
+      <c r="A314" s="74"/>
+      <c r="B314" s="48" t="s">
+        <v>610</v>
+      </c>
+      <c r="C314" s="49" t="s">
+        <v>611</v>
       </c>
       <c r="D314" s="35" t="s">
         <v>26</v>
@@ -11024,12 +11148,12 @@
       <c r="K314" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="315" customHeight="1" ht="18.75">
-      <c r="A315" s="71"/>
-      <c r="B315" s="45" t="s">
-        <v>609</v>
-      </c>
-      <c r="C315" s="46" t="s">
-        <v>610</v>
+      <c r="A315" s="74"/>
+      <c r="B315" s="48" t="s">
+        <v>612</v>
+      </c>
+      <c r="C315" s="49" t="s">
+        <v>613</v>
       </c>
       <c r="D315" s="30" t="s">
         <v>26</v>
@@ -11045,12 +11169,12 @@
       <c r="K315" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="316" customHeight="1" ht="18.75">
-      <c r="A316" s="71"/>
-      <c r="B316" s="45" t="s">
-        <v>611</v>
-      </c>
-      <c r="C316" s="46" t="s">
-        <v>612</v>
+      <c r="A316" s="74"/>
+      <c r="B316" s="48" t="s">
+        <v>614</v>
+      </c>
+      <c r="C316" s="49" t="s">
+        <v>615</v>
       </c>
       <c r="D316" s="35" t="s">
         <v>26</v>
@@ -11066,12 +11190,12 @@
       <c r="K316" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="317" customHeight="1" ht="18.75">
-      <c r="A317" s="71"/>
-      <c r="B317" s="45" t="s">
-        <v>613</v>
-      </c>
-      <c r="C317" s="46" t="s">
-        <v>614</v>
+      <c r="A317" s="74"/>
+      <c r="B317" s="48" t="s">
+        <v>616</v>
+      </c>
+      <c r="C317" s="49" t="s">
+        <v>617</v>
       </c>
       <c r="D317" s="35" t="s">
         <v>26</v>
@@ -11087,12 +11211,12 @@
       <c r="K317" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="318" customHeight="1" ht="18.75">
-      <c r="A318" s="71"/>
-      <c r="B318" s="45" t="s">
-        <v>615</v>
-      </c>
-      <c r="C318" s="46" t="s">
-        <v>616</v>
+      <c r="A318" s="74"/>
+      <c r="B318" s="48" t="s">
+        <v>618</v>
+      </c>
+      <c r="C318" s="49" t="s">
+        <v>619</v>
       </c>
       <c r="D318" s="35" t="s">
         <v>26</v>
@@ -11108,12 +11232,12 @@
       <c r="K318" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="319" customHeight="1" ht="18.75">
-      <c r="A319" s="71"/>
-      <c r="B319" s="45" t="s">
-        <v>617</v>
-      </c>
-      <c r="C319" s="46" t="s">
-        <v>618</v>
+      <c r="A319" s="74"/>
+      <c r="B319" s="48" t="s">
+        <v>620</v>
+      </c>
+      <c r="C319" s="49" t="s">
+        <v>621</v>
       </c>
       <c r="D319" s="35" t="s">
         <v>26</v>
@@ -11130,15 +11254,15 @@
     </row>
     <row x14ac:dyDescent="0.25" r="320" customHeight="1" ht="18.75">
       <c r="A320" s="24" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="B320" s="25" t="s">
-        <v>620</v>
-      </c>
-      <c r="C320" s="56" t="s">
-        <v>621</v>
-      </c>
-      <c r="D320" s="50"/>
+        <v>623</v>
+      </c>
+      <c r="C320" s="59" t="s">
+        <v>624</v>
+      </c>
+      <c r="D320" s="53"/>
       <c r="E320" s="26"/>
       <c r="F320" s="4"/>
       <c r="G320" s="4"/>
@@ -11149,10 +11273,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="321" customHeight="1" ht="18.75">
       <c r="A321" s="41" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="B321" s="30" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C321" s="30"/>
       <c r="D321" s="35" t="s">
@@ -11169,10 +11293,10 @@
     <row x14ac:dyDescent="0.25" r="322" customHeight="1" ht="18.75">
       <c r="A322" s="29"/>
       <c r="B322" s="30" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C322" s="30" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D322" s="35" t="s">
         <v>26</v>
@@ -11190,10 +11314,10 @@
     <row x14ac:dyDescent="0.25" r="323" customHeight="1" ht="18.75">
       <c r="A323" s="29"/>
       <c r="B323" s="30" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="C323" s="30" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D323" s="35" t="s">
         <v>26</v>
@@ -11211,10 +11335,10 @@
     <row x14ac:dyDescent="0.25" r="324" customHeight="1" ht="18.75">
       <c r="A324" s="29"/>
       <c r="B324" s="30" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C324" s="30" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="D324" s="35" t="s">
         <v>26</v>
@@ -11232,10 +11356,10 @@
     <row x14ac:dyDescent="0.25" r="325" customHeight="1" ht="18.75">
       <c r="A325" s="29"/>
       <c r="B325" s="30" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C325" s="30" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="D325" s="35" t="s">
         <v>26</v>
@@ -11253,10 +11377,10 @@
     <row x14ac:dyDescent="0.25" r="326" customHeight="1" ht="18.75">
       <c r="A326" s="29"/>
       <c r="B326" s="30" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="C326" s="30" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="D326" s="43" t="s">
         <v>26</v>
@@ -11273,7 +11397,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="327" customHeight="1" ht="18.75">
       <c r="A327" s="29" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B327" s="30"/>
       <c r="C327" s="30"/>
@@ -11289,10 +11413,10 @@
     <row x14ac:dyDescent="0.25" r="328" customHeight="1" ht="18.75">
       <c r="A328" s="29"/>
       <c r="B328" s="30" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C328" s="30" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="D328" s="30" t="s">
         <v>26</v>
@@ -11310,10 +11434,10 @@
     <row x14ac:dyDescent="0.25" r="329" customHeight="1" ht="18.75">
       <c r="A329" s="29"/>
       <c r="B329" s="43" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C329" s="30" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="D329" s="35" t="s">
         <v>26</v>
@@ -11331,10 +11455,10 @@
     <row x14ac:dyDescent="0.25" r="330" customHeight="1" ht="18.75">
       <c r="A330" s="29"/>
       <c r="B330" s="30" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="C330" s="30" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="D330" s="35" t="s">
         <v>26</v>
@@ -11352,10 +11476,10 @@
     <row x14ac:dyDescent="0.25" r="331" customHeight="1" ht="18.75">
       <c r="A331" s="29"/>
       <c r="B331" s="30" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C331" s="30" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="D331" s="35" t="s">
         <v>26</v>
@@ -11373,10 +11497,10 @@
     <row x14ac:dyDescent="0.25" r="332" customHeight="1" ht="18.75">
       <c r="A332" s="29"/>
       <c r="B332" s="30" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C332" s="30" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="D332" s="35" t="s">
         <v>26</v>
@@ -11393,7 +11517,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="333" customHeight="1" ht="18.75">
       <c r="A333" s="29" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="B333" s="30"/>
       <c r="C333" s="30"/>
@@ -11409,10 +11533,10 @@
     <row x14ac:dyDescent="0.25" r="334" customHeight="1" ht="18.75">
       <c r="A334" s="29"/>
       <c r="B334" s="30" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C334" s="30" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="D334" s="35" t="s">
         <v>26</v>
@@ -11430,10 +11554,10 @@
     <row x14ac:dyDescent="0.25" r="335" customHeight="1" ht="18.75">
       <c r="A335" s="29"/>
       <c r="B335" s="30" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C335" s="30" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="D335" s="35" t="s">
         <v>26</v>
@@ -11450,13 +11574,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="336" customHeight="1" ht="18.75">
       <c r="A336" s="29" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="B336" s="30" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C336" s="30" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="D336" s="35" t="s">
         <v>26</v>
@@ -11474,10 +11598,10 @@
     <row x14ac:dyDescent="0.25" r="337" customHeight="1" ht="18.75">
       <c r="A337" s="29"/>
       <c r="B337" s="30" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="C337" s="30" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="D337" s="35" t="s">
         <v>26</v>
@@ -11495,10 +11619,10 @@
     <row x14ac:dyDescent="0.25" r="338" customHeight="1" ht="18.75">
       <c r="A338" s="29"/>
       <c r="B338" s="30" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C338" s="30" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="D338" s="30" t="s">
         <v>26</v>
@@ -11516,10 +11640,10 @@
     <row x14ac:dyDescent="0.25" r="339" customHeight="1" ht="18.75">
       <c r="A339" s="29"/>
       <c r="B339" s="30" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="C339" s="30" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="D339" s="35" t="s">
         <v>26</v>
@@ -11537,10 +11661,10 @@
     <row x14ac:dyDescent="0.25" r="340" customHeight="1" ht="18.75">
       <c r="A340" s="29"/>
       <c r="B340" s="30" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="C340" s="30" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="D340" s="43" t="s">
         <v>26</v>
@@ -11558,10 +11682,10 @@
     <row x14ac:dyDescent="0.25" r="341" customHeight="1" ht="18.75">
       <c r="A341" s="29"/>
       <c r="B341" s="30" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="C341" s="30" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="D341" s="35" t="s">
         <v>26</v>
@@ -11579,10 +11703,10 @@
     <row x14ac:dyDescent="0.25" r="342" customHeight="1" ht="18.75">
       <c r="A342" s="29"/>
       <c r="B342" s="30" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C342" s="30" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="D342" s="43" t="s">
         <v>26</v>
@@ -11600,10 +11724,10 @@
     <row x14ac:dyDescent="0.25" r="343" customHeight="1" ht="18.75">
       <c r="A343" s="29"/>
       <c r="B343" s="30" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C343" s="30" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="D343" s="35" t="s">
         <v>26</v>
@@ -11621,10 +11745,10 @@
     <row x14ac:dyDescent="0.25" r="344" customHeight="1" ht="18.75">
       <c r="A344" s="29"/>
       <c r="B344" s="30" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C344" s="30" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="D344" s="35" t="s">
         <v>26</v>
@@ -11642,10 +11766,10 @@
     <row x14ac:dyDescent="0.25" r="345" customHeight="1" ht="18.75">
       <c r="A345" s="29"/>
       <c r="B345" s="30" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="C345" s="30" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="D345" s="35" t="s">
         <v>26</v>
@@ -11663,10 +11787,10 @@
     <row x14ac:dyDescent="0.25" r="346" customHeight="1" ht="18.75">
       <c r="A346" s="29"/>
       <c r="B346" s="30" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="C346" s="30" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="D346" s="35" t="s">
         <v>26</v>
@@ -11684,10 +11808,10 @@
     <row x14ac:dyDescent="0.25" r="347" customHeight="1" ht="18.75">
       <c r="A347" s="29"/>
       <c r="B347" s="30" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C347" s="30" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="D347" s="35" t="s">
         <v>26</v>
@@ -11704,9 +11828,9 @@
     </row>
     <row x14ac:dyDescent="0.25" r="348" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A348" s="29" t="s">
-        <v>675</v>
-      </c>
-      <c r="B348" s="74"/>
+        <v>678</v>
+      </c>
+      <c r="B348" s="77"/>
       <c r="C348" s="30"/>
       <c r="D348" s="43"/>
       <c r="E348" s="3"/>
@@ -11720,10 +11844,10 @@
     <row x14ac:dyDescent="0.25" r="349" customHeight="1" ht="18.75">
       <c r="A349" s="29"/>
       <c r="B349" s="30" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C349" s="30" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="D349" s="35" t="s">
         <v>26</v>
@@ -11741,10 +11865,10 @@
     <row x14ac:dyDescent="0.25" r="350" customHeight="1" ht="18.75">
       <c r="A350" s="29"/>
       <c r="B350" s="30" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="C350" s="30" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="D350" s="43" t="s">
         <v>26</v>
@@ -11762,10 +11886,10 @@
     <row x14ac:dyDescent="0.25" r="351" customHeight="1" ht="18.75">
       <c r="A351" s="29"/>
       <c r="B351" s="30" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="C351" s="30" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="D351" s="43" t="s">
         <v>26</v>
@@ -11783,10 +11907,10 @@
     <row x14ac:dyDescent="0.25" r="352" customHeight="1" ht="18.75">
       <c r="A352" s="29"/>
       <c r="B352" s="30" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="C352" s="30" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="D352" s="30" t="s">
         <v>26</v>
@@ -11803,7 +11927,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="353" customHeight="1" ht="18.75">
       <c r="A353" s="29" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="B353" s="30"/>
       <c r="C353" s="30"/>
@@ -11819,10 +11943,10 @@
     <row x14ac:dyDescent="0.25" r="354" customHeight="1" ht="18.75">
       <c r="A354" s="29"/>
       <c r="B354" s="30" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="C354" s="30" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="D354" s="35" t="s">
         <v>26</v>
@@ -11840,10 +11964,10 @@
     <row x14ac:dyDescent="0.25" r="355" customHeight="1" ht="18.75">
       <c r="A355" s="29"/>
       <c r="B355" s="30" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="C355" s="30" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="D355" s="43" t="s">
         <v>26</v>
@@ -11861,10 +11985,10 @@
     <row x14ac:dyDescent="0.25" r="356" customHeight="1" ht="18.75">
       <c r="A356" s="29"/>
       <c r="B356" s="30" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="C356" s="30" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="D356" s="35" t="s">
         <v>26</v>
@@ -11882,10 +12006,10 @@
     <row x14ac:dyDescent="0.25" r="357" customHeight="1" ht="18.75">
       <c r="A357" s="29"/>
       <c r="B357" s="30" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="C357" s="30" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="D357" s="35" t="s">
         <v>26</v>
@@ -11903,10 +12027,10 @@
     <row x14ac:dyDescent="0.25" r="358" customHeight="1" ht="18.75">
       <c r="A358" s="29"/>
       <c r="B358" s="30" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="C358" s="30" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="D358" s="35" t="s">
         <v>26</v>
@@ -11924,10 +12048,10 @@
     <row x14ac:dyDescent="0.25" r="359" customHeight="1" ht="18.75">
       <c r="A359" s="29"/>
       <c r="B359" s="30" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="C359" s="30" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="D359" s="35" t="s">
         <v>26</v>
@@ -11944,7 +12068,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="360" customHeight="1" ht="18.75">
       <c r="A360" s="29" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="B360" s="30"/>
       <c r="C360" s="30"/>
@@ -11960,10 +12084,10 @@
     <row x14ac:dyDescent="0.25" r="361" customHeight="1" ht="18.75">
       <c r="A361" s="29"/>
       <c r="B361" s="30" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="C361" s="30" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="D361" s="35" t="s">
         <v>26</v>
@@ -11981,10 +12105,10 @@
     <row x14ac:dyDescent="0.25" r="362" customHeight="1" ht="18.75">
       <c r="A362" s="29"/>
       <c r="B362" s="30" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="C362" s="30" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="D362" s="35" t="s">
         <v>26</v>
@@ -12002,10 +12126,10 @@
     <row x14ac:dyDescent="0.25" r="363" customHeight="1" ht="18.75">
       <c r="A363" s="29"/>
       <c r="B363" s="30" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="C363" s="30" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="D363" s="43" t="s">
         <v>26</v>
@@ -12023,10 +12147,10 @@
     <row x14ac:dyDescent="0.25" r="364" customHeight="1" ht="18.75">
       <c r="A364" s="29"/>
       <c r="B364" s="30" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="C364" s="30" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="D364" s="43" t="s">
         <v>26</v>
@@ -12044,12 +12168,12 @@
     <row x14ac:dyDescent="0.25" r="365" customHeight="1" ht="18.75">
       <c r="A365" s="29"/>
       <c r="B365" s="30" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="C365" s="30" t="s">
-        <v>707</v>
-      </c>
-      <c r="D365" s="75" t="s">
+        <v>710</v>
+      </c>
+      <c r="D365" s="78" t="s">
         <v>26</v>
       </c>
       <c r="E365" s="31" t="s">
@@ -12064,7 +12188,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="366" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A366" s="29" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="B366" s="30"/>
       <c r="C366" s="30"/>
@@ -12080,7 +12204,7 @@
     <row x14ac:dyDescent="0.25" r="367" customHeight="1" ht="18.75">
       <c r="A367" s="29"/>
       <c r="B367" s="30" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="C367" s="30"/>
       <c r="D367" s="30" t="s">
@@ -12099,7 +12223,7 @@
     <row x14ac:dyDescent="0.25" r="368" customHeight="1" ht="18.75">
       <c r="A368" s="29"/>
       <c r="B368" s="30" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="C368" s="30"/>
       <c r="D368" s="35" t="s">
@@ -12118,10 +12242,10 @@
     <row x14ac:dyDescent="0.25" r="369" customHeight="1" ht="18.75">
       <c r="A369" s="29"/>
       <c r="B369" s="30" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="C369" s="30" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="D369" s="35" t="s">
         <v>26</v>
@@ -12139,10 +12263,10 @@
     <row x14ac:dyDescent="0.25" r="370" customHeight="1" ht="18.75">
       <c r="A370" s="29"/>
       <c r="B370" s="30" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="C370" s="30" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="D370" s="35" t="s">
         <v>26</v>
@@ -12160,10 +12284,10 @@
     <row x14ac:dyDescent="0.25" r="371" customHeight="1" ht="18.75">
       <c r="A371" s="29"/>
       <c r="B371" s="30" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C371" s="30" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="D371" s="43" t="s">
         <v>26</v>
@@ -12181,10 +12305,10 @@
     <row x14ac:dyDescent="0.25" r="372" customHeight="1" ht="18.75">
       <c r="A372" s="29"/>
       <c r="B372" s="30" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="C372" s="30" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="D372" s="43" t="s">
         <v>26</v>
@@ -12202,10 +12326,10 @@
     <row x14ac:dyDescent="0.25" r="373" customHeight="1" ht="18.75">
       <c r="A373" s="29"/>
       <c r="B373" s="30" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="C373" s="30" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="D373" s="35" t="s">
         <v>26</v>
@@ -12223,10 +12347,10 @@
     <row x14ac:dyDescent="0.25" r="374" customHeight="1" ht="18.75">
       <c r="A374" s="29"/>
       <c r="B374" s="30" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="C374" s="30" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="D374" s="35" t="s">
         <v>26</v>
@@ -12243,7 +12367,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="375" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A375" s="29" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="B375" s="30"/>
       <c r="C375" s="30"/>
@@ -12259,10 +12383,10 @@
     <row x14ac:dyDescent="0.25" r="376" customHeight="1" ht="18.75">
       <c r="A376" s="29"/>
       <c r="B376" s="30" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="C376" s="30" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="D376" s="35" t="s">
         <v>26</v>
@@ -12280,10 +12404,10 @@
     <row x14ac:dyDescent="0.25" r="377" customHeight="1" ht="18.75">
       <c r="A377" s="29"/>
       <c r="B377" s="30" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="C377" s="30" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="D377" s="35" t="s">
         <v>26</v>
@@ -12301,10 +12425,10 @@
     <row x14ac:dyDescent="0.25" r="378" customHeight="1" ht="18.75">
       <c r="A378" s="29"/>
       <c r="B378" s="30" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="C378" s="30" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="D378" s="35" t="s">
         <v>26</v>
@@ -12322,10 +12446,10 @@
     <row x14ac:dyDescent="0.25" r="379" customHeight="1" ht="18.75">
       <c r="A379" s="29"/>
       <c r="B379" s="30" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="C379" s="30" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="D379" s="35" t="s">
         <v>26</v>
@@ -12343,10 +12467,10 @@
     <row x14ac:dyDescent="0.25" r="380" customHeight="1" ht="15">
       <c r="A380" s="29"/>
       <c r="B380" s="30" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C380" s="30" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="D380" s="31" t="s">
         <v>26</v>
@@ -12364,10 +12488,10 @@
     <row x14ac:dyDescent="0.25" r="381" customHeight="1" ht="15">
       <c r="A381" s="29"/>
       <c r="B381" s="30" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="C381" s="30" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="D381" s="32" t="s">
         <v>26</v>
@@ -12384,22 +12508,22 @@
     </row>
     <row x14ac:dyDescent="0.25" r="382" customHeight="1" ht="18.75">
       <c r="A382" s="24" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="B382" s="25"/>
       <c r="C382" s="25"/>
       <c r="D382" s="26"/>
-      <c r="E382" s="62"/>
+      <c r="E382" s="65"/>
       <c r="F382" s="4"/>
       <c r="G382" s="4"/>
-      <c r="H382" s="62"/>
-      <c r="I382" s="62"/>
+      <c r="H382" s="65"/>
+      <c r="I382" s="65"/>
       <c r="J382" s="11"/>
       <c r="K382" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="383" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A383" s="29" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="B383" s="30"/>
       <c r="C383" s="30"/>
@@ -12415,10 +12539,10 @@
     <row x14ac:dyDescent="0.25" r="384" customHeight="1" ht="18.75">
       <c r="A384" s="29"/>
       <c r="B384" s="30" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C384" s="30" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="D384" s="35" t="s">
         <v>26</v>
@@ -12436,10 +12560,10 @@
     <row x14ac:dyDescent="0.25" r="385" customHeight="1" ht="18.75">
       <c r="A385" s="29"/>
       <c r="B385" s="30" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="C385" s="30" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="D385" s="43" t="s">
         <v>26</v>
@@ -12457,10 +12581,10 @@
     <row x14ac:dyDescent="0.25" r="386" customHeight="1" ht="18.75">
       <c r="A386" s="29"/>
       <c r="B386" s="30" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="C386" s="30" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="D386" s="43" t="s">
         <v>26</v>
@@ -12478,10 +12602,10 @@
     <row x14ac:dyDescent="0.25" r="387" customHeight="1" ht="18.75">
       <c r="A387" s="29"/>
       <c r="B387" s="30" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="C387" s="30" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="D387" s="43" t="s">
         <v>26</v>
@@ -12499,10 +12623,10 @@
     <row x14ac:dyDescent="0.25" r="388" customHeight="1" ht="18.75">
       <c r="A388" s="29"/>
       <c r="B388" s="30" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="C388" s="30" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="D388" s="43" t="s">
         <v>26</v>
@@ -12520,10 +12644,10 @@
     <row x14ac:dyDescent="0.25" r="389" customHeight="1" ht="18.75">
       <c r="A389" s="29"/>
       <c r="B389" s="30" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="C389" s="30" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="D389" s="35" t="s">
         <v>26</v>
@@ -12541,10 +12665,10 @@
     <row x14ac:dyDescent="0.25" r="390" customHeight="1" ht="18.75">
       <c r="A390" s="29"/>
       <c r="B390" s="30" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="C390" s="30" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="D390" s="35" t="s">
         <v>26</v>
@@ -12562,13 +12686,13 @@
     <row x14ac:dyDescent="0.25" r="391" customHeight="1" ht="18.75">
       <c r="A391" s="29"/>
       <c r="B391" s="30" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="C391" s="30" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="D391" s="31" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="E391" s="31" t="s">
         <v>27</v>
@@ -12583,10 +12707,10 @@
     <row x14ac:dyDescent="0.25" r="392" customHeight="1" ht="18.75">
       <c r="A392" s="29"/>
       <c r="B392" s="30" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="C392" s="30" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="D392" s="43" t="s">
         <v>26</v>
@@ -12604,10 +12728,10 @@
     <row x14ac:dyDescent="0.25" r="393" customHeight="1" ht="18.75">
       <c r="A393" s="29"/>
       <c r="B393" s="30" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="C393" s="30" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="D393" s="35" t="s">
         <v>26</v>
@@ -12625,10 +12749,10 @@
     <row x14ac:dyDescent="0.25" r="394" customHeight="1" ht="18.75">
       <c r="A394" s="29"/>
       <c r="B394" s="30" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="C394" s="30" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="D394" s="35" t="s">
         <v>26</v>
@@ -12646,10 +12770,10 @@
     <row x14ac:dyDescent="0.25" r="395" customHeight="1" ht="18.75">
       <c r="A395" s="29"/>
       <c r="B395" s="30" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="C395" s="30" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="D395" s="35" t="s">
         <v>26</v>
@@ -12667,10 +12791,10 @@
     <row x14ac:dyDescent="0.25" r="396" customHeight="1" ht="18.75">
       <c r="A396" s="29"/>
       <c r="B396" s="30" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="C396" s="30" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="D396" s="35" t="s">
         <v>26</v>
@@ -12688,10 +12812,10 @@
     <row x14ac:dyDescent="0.25" r="397" customHeight="1" ht="18.75">
       <c r="A397" s="29"/>
       <c r="B397" s="30" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="C397" s="30" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="D397" s="35" t="s">
         <v>26</v>
@@ -12709,10 +12833,10 @@
     <row x14ac:dyDescent="0.25" r="398" customHeight="1" ht="18.75">
       <c r="A398" s="29"/>
       <c r="B398" s="30" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="C398" s="30" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D398" s="43" t="s">
         <v>26</v>
@@ -12730,10 +12854,10 @@
     <row x14ac:dyDescent="0.25" r="399" customHeight="1" ht="18.75">
       <c r="A399" s="29"/>
       <c r="B399" s="30" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="C399" s="30" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="D399" s="35" t="s">
         <v>26</v>
@@ -12751,10 +12875,10 @@
     <row x14ac:dyDescent="0.25" r="400" customHeight="1" ht="18.75">
       <c r="A400" s="29"/>
       <c r="B400" s="30" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C400" s="30" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="D400" s="35" t="s">
         <v>26</v>
@@ -12772,10 +12896,10 @@
     <row x14ac:dyDescent="0.25" r="401" customHeight="1" ht="18.75">
       <c r="A401" s="29"/>
       <c r="B401" s="30" t="s">
-        <v>771</v>
-      </c>
-      <c r="C401" s="76" t="s">
-        <v>772</v>
+        <v>774</v>
+      </c>
+      <c r="C401" s="79" t="s">
+        <v>775</v>
       </c>
       <c r="D401" s="43" t="s">
         <v>26</v>
@@ -12793,10 +12917,10 @@
     <row x14ac:dyDescent="0.25" r="402" customHeight="1" ht="18.75">
       <c r="A402" s="29"/>
       <c r="B402" s="30" t="s">
-        <v>773</v>
-      </c>
-      <c r="C402" s="76" t="s">
-        <v>774</v>
+        <v>776</v>
+      </c>
+      <c r="C402" s="79" t="s">
+        <v>777</v>
       </c>
       <c r="D402" s="43" t="s">
         <v>26</v>
@@ -12814,10 +12938,10 @@
     <row x14ac:dyDescent="0.25" r="403" customHeight="1" ht="18.75">
       <c r="A403" s="29"/>
       <c r="B403" s="30" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="C403" s="30" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="D403" s="43" t="s">
         <v>26</v>
@@ -12835,10 +12959,10 @@
     <row x14ac:dyDescent="0.25" r="404" customHeight="1" ht="18.75">
       <c r="A404" s="29"/>
       <c r="B404" s="30" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="C404" s="43" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="D404" s="35" t="s">
         <v>26</v>
@@ -12856,10 +12980,10 @@
     <row x14ac:dyDescent="0.25" r="405" customHeight="1" ht="18.75">
       <c r="A405" s="29"/>
       <c r="B405" s="30" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C405" s="30" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="D405" s="43" t="s">
         <v>26</v>
@@ -12877,10 +13001,10 @@
     <row x14ac:dyDescent="0.25" r="406" customHeight="1" ht="18.75">
       <c r="A406" s="29"/>
       <c r="B406" s="30" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="C406" s="30" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="D406" s="35" t="s">
         <v>26</v>
@@ -12897,13 +13021,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="407" customHeight="1" ht="18.75">
       <c r="A407" s="24" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B407" s="25" t="s">
-        <v>784</v>
-      </c>
-      <c r="C407" s="56" t="s">
-        <v>785</v>
+        <v>787</v>
+      </c>
+      <c r="C407" s="59" t="s">
+        <v>788</v>
       </c>
       <c r="D407" s="26"/>
       <c r="E407" s="26"/>
@@ -12932,10 +13056,10 @@
     <row x14ac:dyDescent="0.25" r="409" customHeight="1" ht="18.75">
       <c r="A409" s="29"/>
       <c r="B409" s="30" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="C409" s="30"/>
-      <c r="D409" s="77" t="s">
+      <c r="D409" s="80" t="s">
         <v>26</v>
       </c>
       <c r="E409" s="32" t="s">
@@ -12950,11 +13074,11 @@
     </row>
     <row x14ac:dyDescent="0.25" r="410" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A410" s="29" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="B410" s="30"/>
       <c r="C410" s="30"/>
-      <c r="D410" s="52"/>
+      <c r="D410" s="55"/>
       <c r="E410" s="3"/>
       <c r="F410" s="3"/>
       <c r="G410" s="3"/>
@@ -12966,12 +13090,12 @@
     <row x14ac:dyDescent="0.25" r="411" customHeight="1" ht="18.75">
       <c r="A411" s="29"/>
       <c r="B411" s="30" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="C411" s="30" t="s">
-        <v>789</v>
-      </c>
-      <c r="D411" s="52" t="s">
+        <v>792</v>
+      </c>
+      <c r="D411" s="55" t="s">
         <v>26</v>
       </c>
       <c r="E411" s="31" t="s">
@@ -12987,12 +13111,12 @@
     <row x14ac:dyDescent="0.25" r="412" customHeight="1" ht="18.75">
       <c r="A412" s="29"/>
       <c r="B412" s="30" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="C412" s="30" t="s">
-        <v>791</v>
-      </c>
-      <c r="D412" s="78" t="s">
+        <v>794</v>
+      </c>
+      <c r="D412" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E412" s="31" t="s">
@@ -13007,13 +13131,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="413" customHeight="1" ht="18.75">
       <c r="A413" s="29"/>
-      <c r="B413" s="75" t="s">
-        <v>792</v>
+      <c r="B413" s="78" t="s">
+        <v>795</v>
       </c>
       <c r="C413" s="30" t="s">
-        <v>793</v>
-      </c>
-      <c r="D413" s="78" t="s">
+        <v>796</v>
+      </c>
+      <c r="D413" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E413" s="31" t="s">
@@ -13029,12 +13153,12 @@
     <row x14ac:dyDescent="0.25" r="414" customHeight="1" ht="18.75">
       <c r="A414" s="29"/>
       <c r="B414" s="30" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="C414" s="30" t="s">
-        <v>795</v>
-      </c>
-      <c r="D414" s="52"/>
+        <v>798</v>
+      </c>
+      <c r="D414" s="55"/>
       <c r="E414" s="31" t="s">
         <v>27</v>
       </c>
@@ -13048,12 +13172,12 @@
     <row x14ac:dyDescent="0.25" r="415" customHeight="1" ht="18.75">
       <c r="A415" s="29"/>
       <c r="B415" s="30" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="C415" s="30" t="s">
-        <v>797</v>
-      </c>
-      <c r="D415" s="78" t="s">
+        <v>800</v>
+      </c>
+      <c r="D415" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E415" s="32" t="s">
@@ -13068,11 +13192,11 @@
     </row>
     <row x14ac:dyDescent="0.25" r="416" customHeight="1" ht="18.75">
       <c r="A416" s="29" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="B416" s="30"/>
       <c r="C416" s="30"/>
-      <c r="D416" s="52"/>
+      <c r="D416" s="55"/>
       <c r="E416" s="32" t="s">
         <v>27</v>
       </c>
@@ -13086,12 +13210,12 @@
     <row x14ac:dyDescent="0.25" r="417" customHeight="1" ht="18.75">
       <c r="A417" s="29"/>
       <c r="B417" s="30" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C417" s="30" t="s">
-        <v>800</v>
-      </c>
-      <c r="D417" s="78" t="s">
+        <v>803</v>
+      </c>
+      <c r="D417" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E417" s="31" t="s">
@@ -13107,12 +13231,12 @@
     <row x14ac:dyDescent="0.25" r="418" customHeight="1" ht="18.75">
       <c r="A418" s="29"/>
       <c r="B418" s="30" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="C418" s="30" t="s">
-        <v>802</v>
-      </c>
-      <c r="D418" s="78" t="s">
+        <v>805</v>
+      </c>
+      <c r="D418" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E418" s="32" t="s">
@@ -13128,12 +13252,12 @@
     <row x14ac:dyDescent="0.25" r="419" customHeight="1" ht="18.75">
       <c r="A419" s="29"/>
       <c r="B419" s="30" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="C419" s="30" t="s">
-        <v>804</v>
-      </c>
-      <c r="D419" s="52" t="s">
+        <v>807</v>
+      </c>
+      <c r="D419" s="55" t="s">
         <v>26</v>
       </c>
       <c r="E419" s="31" t="s">
@@ -13149,12 +13273,12 @@
     <row x14ac:dyDescent="0.25" r="420" customHeight="1" ht="18.75">
       <c r="A420" s="29"/>
       <c r="B420" s="30" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="C420" s="30" t="s">
-        <v>806</v>
-      </c>
-      <c r="D420" s="78" t="s">
+        <v>809</v>
+      </c>
+      <c r="D420" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E420" s="32" t="s">
@@ -13170,12 +13294,12 @@
     <row x14ac:dyDescent="0.25" r="421" customHeight="1" ht="18.75">
       <c r="A421" s="29"/>
       <c r="B421" s="30" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="C421" s="30" t="s">
-        <v>808</v>
-      </c>
-      <c r="D421" s="52" t="s">
+        <v>811</v>
+      </c>
+      <c r="D421" s="55" t="s">
         <v>26</v>
       </c>
       <c r="E421" s="31" t="s">
@@ -13191,12 +13315,12 @@
     <row x14ac:dyDescent="0.25" r="422" customHeight="1" ht="18.75">
       <c r="A422" s="29"/>
       <c r="B422" s="30" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="C422" s="30" t="s">
-        <v>810</v>
-      </c>
-      <c r="D422" s="78" t="s">
+        <v>813</v>
+      </c>
+      <c r="D422" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E422" s="32" t="s">
@@ -13212,12 +13336,12 @@
     <row x14ac:dyDescent="0.25" r="423" customHeight="1" ht="18.75">
       <c r="A423" s="29"/>
       <c r="B423" s="30" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="C423" s="30" t="s">
-        <v>812</v>
-      </c>
-      <c r="D423" s="75" t="s">
+        <v>815</v>
+      </c>
+      <c r="D423" s="78" t="s">
         <v>26</v>
       </c>
       <c r="E423" s="31" t="s">
@@ -13233,10 +13357,10 @@
     <row x14ac:dyDescent="0.25" r="424" customHeight="1" ht="18.75">
       <c r="A424" s="29"/>
       <c r="B424" s="30" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="C424" s="30" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="D424" s="41" t="s">
         <v>26</v>
@@ -13254,12 +13378,12 @@
     <row x14ac:dyDescent="0.25" r="425" customHeight="1" ht="18.75">
       <c r="A425" s="29"/>
       <c r="B425" s="30" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C425" s="30" t="s">
-        <v>816</v>
-      </c>
-      <c r="D425" s="75" t="s">
+        <v>819</v>
+      </c>
+      <c r="D425" s="78" t="s">
         <v>26</v>
       </c>
       <c r="E425" s="32" t="s">
@@ -13274,7 +13398,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="426" customHeight="1" ht="18.75">
       <c r="A426" s="29" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="B426" s="30"/>
       <c r="C426" s="30"/>
@@ -13290,16 +13414,16 @@
     <row x14ac:dyDescent="0.25" r="427" customHeight="1" ht="18.75">
       <c r="A427" s="29"/>
       <c r="B427" s="30" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C427" s="30" t="s">
-        <v>819</v>
-      </c>
-      <c r="D427" s="77" t="s">
+        <v>822</v>
+      </c>
+      <c r="D427" s="80" t="s">
         <v>26</v>
       </c>
       <c r="E427" s="32" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F427" s="4"/>
       <c r="G427" s="4"/>
@@ -13311,16 +13435,16 @@
     <row x14ac:dyDescent="0.25" r="428" customHeight="1" ht="18.75">
       <c r="A428" s="29"/>
       <c r="B428" s="30" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="C428" s="30" t="s">
-        <v>821</v>
-      </c>
-      <c r="D428" s="78" t="s">
+        <v>824</v>
+      </c>
+      <c r="D428" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E428" s="32" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F428" s="4"/>
       <c r="G428" s="4"/>
@@ -13332,12 +13456,12 @@
     <row x14ac:dyDescent="0.25" r="429" customHeight="1" ht="18.75">
       <c r="A429" s="29"/>
       <c r="B429" s="30" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="C429" s="30" t="s">
-        <v>823</v>
-      </c>
-      <c r="D429" s="78" t="s">
+        <v>826</v>
+      </c>
+      <c r="D429" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E429" s="31" t="s">
@@ -13353,12 +13477,12 @@
     <row x14ac:dyDescent="0.25" r="430" customHeight="1" ht="18.75">
       <c r="A430" s="29"/>
       <c r="B430" s="30" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="C430" s="30" t="s">
-        <v>825</v>
-      </c>
-      <c r="D430" s="78" t="s">
+        <v>828</v>
+      </c>
+      <c r="D430" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E430" s="32" t="s">
@@ -13374,10 +13498,10 @@
     <row x14ac:dyDescent="0.25" r="431" customHeight="1" ht="18.75">
       <c r="A431" s="29"/>
       <c r="B431" s="30" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="C431" s="30"/>
-      <c r="D431" s="78" t="s">
+      <c r="D431" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E431" s="32" t="s">
@@ -13393,12 +13517,12 @@
     <row x14ac:dyDescent="0.25" r="432" customHeight="1" ht="18.75">
       <c r="A432" s="29"/>
       <c r="B432" s="30" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="C432" s="30" t="s">
-        <v>828</v>
-      </c>
-      <c r="D432" s="78" t="s">
+        <v>831</v>
+      </c>
+      <c r="D432" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E432" s="31" t="s">
@@ -13414,12 +13538,12 @@
     <row x14ac:dyDescent="0.25" r="433" customHeight="1" ht="18.75">
       <c r="A433" s="29"/>
       <c r="B433" s="30" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="C433" s="30" t="s">
-        <v>830</v>
-      </c>
-      <c r="D433" s="78" t="s">
+        <v>833</v>
+      </c>
+      <c r="D433" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E433" s="32" t="s">
@@ -13435,12 +13559,12 @@
     <row x14ac:dyDescent="0.25" r="434" customHeight="1" ht="18.75">
       <c r="A434" s="29"/>
       <c r="B434" s="30" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="C434" s="30" t="s">
-        <v>832</v>
-      </c>
-      <c r="D434" s="78" t="s">
+        <v>835</v>
+      </c>
+      <c r="D434" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E434" s="31" t="s">
@@ -13456,12 +13580,12 @@
     <row x14ac:dyDescent="0.25" r="435" customHeight="1" ht="18.75">
       <c r="A435" s="29"/>
       <c r="B435" s="30" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="C435" s="30" t="s">
-        <v>834</v>
-      </c>
-      <c r="D435" s="78" t="s">
+        <v>837</v>
+      </c>
+      <c r="D435" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E435" s="31" t="s">
@@ -13477,12 +13601,12 @@
     <row x14ac:dyDescent="0.25" r="436" customHeight="1" ht="18.75">
       <c r="A436" s="29"/>
       <c r="B436" s="30" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="C436" s="30" t="s">
-        <v>836</v>
-      </c>
-      <c r="D436" s="78" t="s">
+        <v>839</v>
+      </c>
+      <c r="D436" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E436" s="32" t="s">
@@ -13498,12 +13622,12 @@
     <row x14ac:dyDescent="0.25" r="437" customHeight="1" ht="18.75">
       <c r="A437" s="29"/>
       <c r="B437" s="30" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="C437" s="30" t="s">
-        <v>838</v>
-      </c>
-      <c r="D437" s="78" t="s">
+        <v>841</v>
+      </c>
+      <c r="D437" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E437" s="32"/>
@@ -13517,12 +13641,12 @@
     <row x14ac:dyDescent="0.25" r="438" customHeight="1" ht="18.75">
       <c r="A438" s="29"/>
       <c r="B438" s="30" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="C438" s="30" t="s">
-        <v>840</v>
-      </c>
-      <c r="D438" s="52" t="s">
+        <v>843</v>
+      </c>
+      <c r="D438" s="55" t="s">
         <v>26</v>
       </c>
       <c r="E438" s="32" t="s">
@@ -13538,12 +13662,12 @@
     <row x14ac:dyDescent="0.25" r="439" customHeight="1" ht="18.75">
       <c r="A439" s="29"/>
       <c r="B439" s="30" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="C439" s="30" t="s">
-        <v>842</v>
-      </c>
-      <c r="D439" s="78" t="s">
+        <v>845</v>
+      </c>
+      <c r="D439" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E439" s="31" t="s">
@@ -13558,7 +13682,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="440" customHeight="1" ht="18.75">
       <c r="A440" s="29" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="B440" s="30"/>
       <c r="C440" s="30"/>
@@ -13576,12 +13700,12 @@
     <row x14ac:dyDescent="0.25" r="441" customHeight="1" ht="18.75">
       <c r="A441" s="29"/>
       <c r="B441" s="30" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="C441" s="30" t="s">
-        <v>845</v>
-      </c>
-      <c r="D441" s="78" t="s">
+        <v>848</v>
+      </c>
+      <c r="D441" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E441" s="32" t="s">
@@ -13597,10 +13721,10 @@
     <row x14ac:dyDescent="0.25" r="442" customHeight="1" ht="18.75">
       <c r="A442" s="29"/>
       <c r="B442" s="30" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="C442" s="30"/>
-      <c r="D442" s="78" t="s">
+      <c r="D442" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E442" s="32" t="s">
@@ -13616,12 +13740,12 @@
     <row x14ac:dyDescent="0.25" r="443" customHeight="1" ht="18.75">
       <c r="A443" s="29"/>
       <c r="B443" s="30" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="C443" s="30" t="s">
-        <v>848</v>
-      </c>
-      <c r="D443" s="78" t="s">
+        <v>851</v>
+      </c>
+      <c r="D443" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E443" s="31" t="s">
@@ -13637,12 +13761,12 @@
     <row x14ac:dyDescent="0.25" r="444" customHeight="1" ht="18.75">
       <c r="A444" s="29"/>
       <c r="B444" s="30" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="C444" s="30" t="s">
-        <v>850</v>
-      </c>
-      <c r="D444" s="78" t="s">
+        <v>853</v>
+      </c>
+      <c r="D444" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E444" s="32" t="s">
@@ -13658,12 +13782,12 @@
     <row x14ac:dyDescent="0.25" r="445" customHeight="1" ht="18.75">
       <c r="A445" s="29"/>
       <c r="B445" s="30" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="C445" s="30" t="s">
-        <v>852</v>
-      </c>
-      <c r="D445" s="78" t="s">
+        <v>855</v>
+      </c>
+      <c r="D445" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E445" s="32" t="s">
@@ -13679,12 +13803,12 @@
     <row x14ac:dyDescent="0.25" r="446" customHeight="1" ht="18.75">
       <c r="A446" s="29"/>
       <c r="B446" s="30" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C446" s="30" t="s">
-        <v>854</v>
-      </c>
-      <c r="D446" s="78" t="s">
+        <v>857</v>
+      </c>
+      <c r="D446" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E446" s="32" t="s">
@@ -13699,11 +13823,11 @@
     </row>
     <row x14ac:dyDescent="0.25" r="447" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A447" s="29" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="B447" s="30"/>
       <c r="C447" s="30"/>
-      <c r="D447" s="52"/>
+      <c r="D447" s="55"/>
       <c r="E447" s="3"/>
       <c r="F447" s="3"/>
       <c r="G447" s="3"/>
@@ -13715,12 +13839,12 @@
     <row x14ac:dyDescent="0.25" r="448" customHeight="1" ht="18.75">
       <c r="A448" s="29"/>
       <c r="B448" s="30" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="C448" s="30" t="s">
-        <v>857</v>
-      </c>
-      <c r="D448" s="78" t="s">
+        <v>860</v>
+      </c>
+      <c r="D448" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E448" s="31" t="s">
@@ -13736,12 +13860,12 @@
     <row x14ac:dyDescent="0.25" r="449" customHeight="1" ht="18.75">
       <c r="A449" s="29"/>
       <c r="B449" s="30" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="C449" s="30" t="s">
-        <v>859</v>
-      </c>
-      <c r="D449" s="78" t="s">
+        <v>862</v>
+      </c>
+      <c r="D449" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E449" s="31" t="s">
@@ -13757,12 +13881,12 @@
     <row x14ac:dyDescent="0.25" r="450" customHeight="1" ht="18.75">
       <c r="A450" s="29"/>
       <c r="B450" s="30" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C450" s="30" t="s">
-        <v>861</v>
-      </c>
-      <c r="D450" s="78" t="s">
+        <v>864</v>
+      </c>
+      <c r="D450" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E450" s="31" t="s">
@@ -13778,12 +13902,12 @@
     <row x14ac:dyDescent="0.25" r="451" customHeight="1" ht="18.75">
       <c r="A451" s="29"/>
       <c r="B451" s="30" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="C451" s="30" t="s">
-        <v>863</v>
-      </c>
-      <c r="D451" s="78" t="s">
+        <v>866</v>
+      </c>
+      <c r="D451" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E451" s="31" t="s">
@@ -13799,12 +13923,12 @@
     <row x14ac:dyDescent="0.25" r="452" customHeight="1" ht="18.75">
       <c r="A452" s="29"/>
       <c r="B452" s="30" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="C452" s="30" t="s">
-        <v>865</v>
-      </c>
-      <c r="D452" s="78" t="s">
+        <v>868</v>
+      </c>
+      <c r="D452" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E452" s="31" t="s">
@@ -13820,12 +13944,12 @@
     <row x14ac:dyDescent="0.25" r="453" customHeight="1" ht="18.75">
       <c r="A453" s="29"/>
       <c r="B453" s="30" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="C453" s="30" t="s">
-        <v>867</v>
-      </c>
-      <c r="D453" s="78" t="s">
+        <v>870</v>
+      </c>
+      <c r="D453" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E453" s="31" t="s">
@@ -13841,12 +13965,12 @@
     <row x14ac:dyDescent="0.25" r="454" customHeight="1" ht="18.75">
       <c r="A454" s="29"/>
       <c r="B454" s="30" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C454" s="30" t="s">
-        <v>869</v>
-      </c>
-      <c r="D454" s="78" t="s">
+        <v>872</v>
+      </c>
+      <c r="D454" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E454" s="31" t="s">
@@ -13862,12 +13986,12 @@
     <row x14ac:dyDescent="0.25" r="455" customHeight="1" ht="18.75">
       <c r="A455" s="29"/>
       <c r="B455" s="30" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="C455" s="30" t="s">
-        <v>871</v>
-      </c>
-      <c r="D455" s="78" t="s">
+        <v>874</v>
+      </c>
+      <c r="D455" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E455" s="31" t="s">
@@ -13883,12 +14007,12 @@
     <row x14ac:dyDescent="0.25" r="456" customHeight="1" ht="18.75">
       <c r="A456" s="29"/>
       <c r="B456" s="30" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="C456" s="30" t="s">
-        <v>873</v>
-      </c>
-      <c r="D456" s="78" t="s">
+        <v>876</v>
+      </c>
+      <c r="D456" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E456" s="31" t="s">
@@ -13903,13 +14027,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="457" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A457" s="29" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="B457" s="30" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="C457" s="30"/>
-      <c r="D457" s="52"/>
+      <c r="D457" s="55"/>
       <c r="E457" s="3"/>
       <c r="F457" s="3"/>
       <c r="G457" s="3"/>
@@ -13921,12 +14045,12 @@
     <row x14ac:dyDescent="0.25" r="458" customHeight="1" ht="18.75">
       <c r="A458" s="29"/>
       <c r="B458" s="30" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="C458" s="30" t="s">
-        <v>877</v>
-      </c>
-      <c r="D458" s="78" t="s">
+        <v>880</v>
+      </c>
+      <c r="D458" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E458" s="31" t="s">
@@ -13942,12 +14066,12 @@
     <row x14ac:dyDescent="0.25" r="459" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A459" s="29"/>
       <c r="B459" s="30" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="C459" s="30" t="s">
-        <v>879</v>
-      </c>
-      <c r="D459" s="78" t="s">
+        <v>882</v>
+      </c>
+      <c r="D459" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E459" s="3"/>
@@ -13961,12 +14085,12 @@
     <row x14ac:dyDescent="0.25" r="460" customHeight="1" ht="18.75">
       <c r="A460" s="29"/>
       <c r="B460" s="30" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="C460" s="30" t="s">
-        <v>881</v>
-      </c>
-      <c r="D460" s="78" t="s">
+        <v>884</v>
+      </c>
+      <c r="D460" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E460" s="31" t="s">
@@ -13982,12 +14106,12 @@
     <row x14ac:dyDescent="0.25" r="461" customHeight="1" ht="18.75">
       <c r="A461" s="29"/>
       <c r="B461" s="30" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="C461" s="30" t="s">
-        <v>883</v>
-      </c>
-      <c r="D461" s="78" t="s">
+        <v>886</v>
+      </c>
+      <c r="D461" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E461" s="31" t="s">
@@ -14003,12 +14127,12 @@
     <row x14ac:dyDescent="0.25" r="462" customHeight="1" ht="18.75">
       <c r="A462" s="29"/>
       <c r="B462" s="30" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="C462" s="30" t="s">
-        <v>885</v>
-      </c>
-      <c r="D462" s="78" t="s">
+        <v>888</v>
+      </c>
+      <c r="D462" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E462" s="31" t="s">
@@ -14024,12 +14148,12 @@
     <row x14ac:dyDescent="0.25" r="463" customHeight="1" ht="18.75">
       <c r="A463" s="29"/>
       <c r="B463" s="30" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="C463" s="30" t="s">
-        <v>887</v>
-      </c>
-      <c r="D463" s="52"/>
+        <v>890</v>
+      </c>
+      <c r="D463" s="55"/>
       <c r="E463" s="31" t="s">
         <v>27</v>
       </c>
@@ -14043,12 +14167,12 @@
     <row x14ac:dyDescent="0.25" r="464" customHeight="1" ht="18.75">
       <c r="A464" s="29"/>
       <c r="B464" s="30" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C464" s="30" t="s">
-        <v>889</v>
-      </c>
-      <c r="D464" s="78" t="s">
+        <v>892</v>
+      </c>
+      <c r="D464" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E464" s="31" t="s">
@@ -14064,12 +14188,12 @@
     <row x14ac:dyDescent="0.25" r="465" customHeight="1" ht="18.75">
       <c r="A465" s="29"/>
       <c r="B465" s="30" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="C465" s="30" t="s">
-        <v>891</v>
-      </c>
-      <c r="D465" s="78" t="s">
+        <v>894</v>
+      </c>
+      <c r="D465" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E465" s="31" t="s">
@@ -14084,11 +14208,11 @@
     </row>
     <row x14ac:dyDescent="0.25" r="466" customHeight="1" ht="18.75">
       <c r="A466" s="29" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="B466" s="30"/>
       <c r="C466" s="30"/>
-      <c r="D466" s="52"/>
+      <c r="D466" s="55"/>
       <c r="E466" s="32"/>
       <c r="F466" s="4"/>
       <c r="G466" s="4"/>
@@ -14100,12 +14224,12 @@
     <row x14ac:dyDescent="0.25" r="467" customHeight="1" ht="18.75">
       <c r="A467" s="29"/>
       <c r="B467" s="30" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="C467" s="30" t="s">
-        <v>894</v>
-      </c>
-      <c r="D467" s="78" t="s">
+        <v>897</v>
+      </c>
+      <c r="D467" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E467" s="32" t="s">
@@ -14120,13 +14244,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="468" customHeight="1" ht="18.75">
       <c r="A468" s="29"/>
-      <c r="B468" s="75" t="s">
-        <v>895</v>
+      <c r="B468" s="78" t="s">
+        <v>898</v>
       </c>
       <c r="C468" s="30" t="s">
-        <v>896</v>
-      </c>
-      <c r="D468" s="78" t="s">
+        <v>899</v>
+      </c>
+      <c r="D468" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E468" s="32" t="s">
@@ -14142,12 +14266,12 @@
     <row x14ac:dyDescent="0.25" r="469" customHeight="1" ht="18.75">
       <c r="A469" s="29"/>
       <c r="B469" s="30" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="C469" s="30" t="s">
-        <v>898</v>
-      </c>
-      <c r="D469" s="78" t="s">
+        <v>901</v>
+      </c>
+      <c r="D469" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E469" s="32" t="s">
@@ -14162,13 +14286,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="470" customHeight="1" ht="18.75">
       <c r="A470" s="29"/>
-      <c r="B470" s="75" t="s">
-        <v>899</v>
+      <c r="B470" s="78" t="s">
+        <v>902</v>
       </c>
       <c r="C470" s="30" t="s">
-        <v>900</v>
-      </c>
-      <c r="D470" s="78" t="s">
+        <v>903</v>
+      </c>
+      <c r="D470" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E470" s="32" t="s">
@@ -14184,12 +14308,12 @@
     <row x14ac:dyDescent="0.25" r="471" customHeight="1" ht="18.75">
       <c r="A471" s="29"/>
       <c r="B471" s="30" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="C471" s="30" t="s">
-        <v>902</v>
-      </c>
-      <c r="D471" s="78" t="s">
+        <v>905</v>
+      </c>
+      <c r="D471" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E471" s="32" t="s">
@@ -14204,13 +14328,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="472" customHeight="1" ht="18.75">
       <c r="A472" s="29"/>
-      <c r="B472" s="75" t="s">
-        <v>903</v>
+      <c r="B472" s="78" t="s">
+        <v>906</v>
       </c>
       <c r="C472" s="30" t="s">
-        <v>904</v>
-      </c>
-      <c r="D472" s="78" t="s">
+        <v>907</v>
+      </c>
+      <c r="D472" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E472" s="32" t="s">
@@ -14225,7 +14349,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="473" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A473" s="29" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="B473" s="30"/>
       <c r="C473" s="30"/>
@@ -14241,12 +14365,12 @@
     <row x14ac:dyDescent="0.25" r="474" customHeight="1" ht="18.75">
       <c r="A474" s="29"/>
       <c r="B474" s="30" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="C474" s="30" t="s">
-        <v>907</v>
-      </c>
-      <c r="D474" s="78" t="s">
+        <v>910</v>
+      </c>
+      <c r="D474" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E474" s="31" t="s">
@@ -14262,12 +14386,12 @@
     <row x14ac:dyDescent="0.25" r="475" customHeight="1" ht="18.75">
       <c r="A475" s="29"/>
       <c r="B475" s="30" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="C475" s="30" t="s">
-        <v>909</v>
-      </c>
-      <c r="D475" s="78" t="s">
+        <v>912</v>
+      </c>
+      <c r="D475" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E475" s="31" t="s">
@@ -14283,12 +14407,12 @@
     <row x14ac:dyDescent="0.25" r="476" customHeight="1" ht="18.75">
       <c r="A476" s="29"/>
       <c r="B476" s="30" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="C476" s="30" t="s">
-        <v>911</v>
-      </c>
-      <c r="D476" s="78" t="s">
+        <v>914</v>
+      </c>
+      <c r="D476" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E476" s="31" t="s">
@@ -14304,12 +14428,12 @@
     <row x14ac:dyDescent="0.25" r="477" customHeight="1" ht="18.75">
       <c r="A477" s="29"/>
       <c r="B477" s="30" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="C477" s="30" t="s">
-        <v>913</v>
-      </c>
-      <c r="D477" s="78" t="s">
+        <v>916</v>
+      </c>
+      <c r="D477" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E477" s="31" t="s">
@@ -14325,12 +14449,12 @@
     <row x14ac:dyDescent="0.25" r="478" customHeight="1" ht="18.75">
       <c r="A478" s="29"/>
       <c r="B478" s="30" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="C478" s="30" t="s">
-        <v>915</v>
-      </c>
-      <c r="D478" s="78" t="s">
+        <v>918</v>
+      </c>
+      <c r="D478" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E478" s="31" t="s">
@@ -14346,12 +14470,12 @@
     <row x14ac:dyDescent="0.25" r="479" customHeight="1" ht="18.75">
       <c r="A479" s="29"/>
       <c r="B479" s="30" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="C479" s="30" t="s">
-        <v>917</v>
-      </c>
-      <c r="D479" s="78" t="s">
+        <v>920</v>
+      </c>
+      <c r="D479" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E479" s="31" t="s">
@@ -14367,12 +14491,12 @@
     <row x14ac:dyDescent="0.25" r="480" customHeight="1" ht="18.75">
       <c r="A480" s="29"/>
       <c r="B480" s="30" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="C480" s="30" t="s">
-        <v>919</v>
-      </c>
-      <c r="D480" s="78" t="s">
+        <v>922</v>
+      </c>
+      <c r="D480" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E480" s="31" t="s">
@@ -14388,12 +14512,12 @@
     <row x14ac:dyDescent="0.25" r="481" customHeight="1" ht="18.75">
       <c r="A481" s="29"/>
       <c r="B481" s="30" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="C481" s="30" t="s">
-        <v>921</v>
-      </c>
-      <c r="D481" s="78" t="s">
+        <v>924</v>
+      </c>
+      <c r="D481" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E481" s="32" t="s">
@@ -14408,26 +14532,26 @@
     </row>
     <row x14ac:dyDescent="0.25" r="482" customHeight="1" ht="18.75">
       <c r="A482" s="24" t="s">
-        <v>922</v>
-      </c>
-      <c r="B482" s="61"/>
-      <c r="C482" s="61"/>
-      <c r="D482" s="79"/>
-      <c r="E482" s="62"/>
+        <v>925</v>
+      </c>
+      <c r="B482" s="64"/>
+      <c r="C482" s="64"/>
+      <c r="D482" s="82"/>
+      <c r="E482" s="65"/>
       <c r="F482" s="4"/>
       <c r="G482" s="4"/>
-      <c r="H482" s="62"/>
-      <c r="I482" s="62"/>
+      <c r="H482" s="65"/>
+      <c r="I482" s="65"/>
       <c r="J482" s="11"/>
       <c r="K482" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="483" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A483" s="29" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B483" s="30"/>
       <c r="C483" s="30"/>
-      <c r="D483" s="52"/>
+      <c r="D483" s="55"/>
       <c r="E483" s="3"/>
       <c r="F483" s="3"/>
       <c r="G483" s="3"/>
@@ -14439,31 +14563,31 @@
     <row x14ac:dyDescent="0.25" r="484" customHeight="1" ht="18.75">
       <c r="A484" s="29"/>
       <c r="B484" s="30" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="C484" s="30"/>
-      <c r="D484" s="78" t="s">
-        <v>26</v>
-      </c>
-      <c r="E484" s="75" t="s">
+      <c r="D484" s="81" t="s">
+        <v>26</v>
+      </c>
+      <c r="E484" s="78" t="s">
         <v>27</v>
       </c>
       <c r="F484" s="4"/>
       <c r="G484" s="4"/>
-      <c r="H484" s="75"/>
-      <c r="I484" s="75"/>
+      <c r="H484" s="78"/>
+      <c r="I484" s="78"/>
       <c r="J484" s="11"/>
       <c r="K484" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="485" customHeight="1" ht="18.75">
       <c r="A485" s="29"/>
       <c r="B485" s="30" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="C485" s="30" t="s">
-        <v>925</v>
-      </c>
-      <c r="D485" s="78" t="s">
+        <v>928</v>
+      </c>
+      <c r="D485" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E485" s="31" t="s">
@@ -14479,12 +14603,12 @@
     <row x14ac:dyDescent="0.25" r="486" customHeight="1" ht="18.75">
       <c r="A486" s="29"/>
       <c r="B486" s="30" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="C486" s="30" t="s">
-        <v>927</v>
-      </c>
-      <c r="D486" s="78" t="s">
+        <v>930</v>
+      </c>
+      <c r="D486" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E486" s="31" t="s">
@@ -14500,12 +14624,12 @@
     <row x14ac:dyDescent="0.25" r="487" customHeight="1" ht="18.75">
       <c r="A487" s="29"/>
       <c r="B487" s="30" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="C487" s="30" t="s">
-        <v>929</v>
-      </c>
-      <c r="D487" s="78" t="s">
+        <v>932</v>
+      </c>
+      <c r="D487" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E487" s="31" t="s">
@@ -14520,11 +14644,11 @@
     </row>
     <row x14ac:dyDescent="0.25" r="488" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A488" s="29" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="B488" s="30"/>
       <c r="C488" s="30"/>
-      <c r="D488" s="52"/>
+      <c r="D488" s="55"/>
       <c r="E488" s="3"/>
       <c r="F488" s="3"/>
       <c r="G488" s="3"/>
@@ -14536,12 +14660,12 @@
     <row x14ac:dyDescent="0.25" r="489" customHeight="1" ht="18.75">
       <c r="A489" s="29"/>
       <c r="B489" s="30" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="C489" s="30" t="s">
-        <v>932</v>
-      </c>
-      <c r="D489" s="78" t="s">
+        <v>935</v>
+      </c>
+      <c r="D489" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E489" s="41" t="s">
@@ -14549,18 +14673,18 @@
       </c>
       <c r="F489" s="4"/>
       <c r="G489" s="4"/>
-      <c r="H489" s="75"/>
-      <c r="I489" s="75"/>
+      <c r="H489" s="78"/>
+      <c r="I489" s="78"/>
       <c r="J489" s="11"/>
       <c r="K489" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="490" customHeight="1" ht="18.75">
       <c r="A490" s="29"/>
       <c r="B490" s="30" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="C490" s="30"/>
-      <c r="D490" s="78" t="s">
+      <c r="D490" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E490" s="32" t="s">
@@ -14576,12 +14700,12 @@
     <row x14ac:dyDescent="0.25" r="491" customHeight="1" ht="18.75">
       <c r="A491" s="29"/>
       <c r="B491" s="30" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="C491" s="30" t="s">
-        <v>935</v>
-      </c>
-      <c r="D491" s="78" t="s">
+        <v>938</v>
+      </c>
+      <c r="D491" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E491" s="32" t="s">
@@ -14597,12 +14721,12 @@
     <row x14ac:dyDescent="0.25" r="492" customHeight="1" ht="18.75">
       <c r="A492" s="29"/>
       <c r="B492" s="30" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="C492" s="30" t="s">
-        <v>937</v>
-      </c>
-      <c r="D492" s="78" t="s">
+        <v>940</v>
+      </c>
+      <c r="D492" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E492" s="32" t="s">
@@ -14618,12 +14742,12 @@
     <row x14ac:dyDescent="0.25" r="493" customHeight="1" ht="18.75">
       <c r="A493" s="29"/>
       <c r="B493" s="30" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="C493" s="30" t="s">
-        <v>939</v>
-      </c>
-      <c r="D493" s="78" t="s">
+        <v>942</v>
+      </c>
+      <c r="D493" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E493" s="32" t="s">
@@ -14639,12 +14763,12 @@
     <row x14ac:dyDescent="0.25" r="494" customHeight="1" ht="18.75">
       <c r="A494" s="29"/>
       <c r="B494" s="30" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="C494" s="30" t="s">
-        <v>941</v>
-      </c>
-      <c r="D494" s="78" t="s">
+        <v>944</v>
+      </c>
+      <c r="D494" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E494" s="31" t="s">
@@ -14660,12 +14784,12 @@
     <row x14ac:dyDescent="0.25" r="495" customHeight="1" ht="18.75">
       <c r="A495" s="29"/>
       <c r="B495" s="30" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="C495" s="30" t="s">
-        <v>943</v>
-      </c>
-      <c r="D495" s="78" t="s">
+        <v>946</v>
+      </c>
+      <c r="D495" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E495" s="32" t="s">
@@ -14681,12 +14805,12 @@
     <row x14ac:dyDescent="0.25" r="496" customHeight="1" ht="18.75">
       <c r="A496" s="29"/>
       <c r="B496" s="30" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="C496" s="30" t="s">
-        <v>945</v>
-      </c>
-      <c r="D496" s="78" t="s">
+        <v>948</v>
+      </c>
+      <c r="D496" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E496" s="32" t="s">
@@ -14702,12 +14826,12 @@
     <row x14ac:dyDescent="0.25" r="497" customHeight="1" ht="18.75">
       <c r="A497" s="29"/>
       <c r="B497" s="30" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="C497" s="30" t="s">
-        <v>947</v>
-      </c>
-      <c r="D497" s="52" t="s">
+        <v>950</v>
+      </c>
+      <c r="D497" s="55" t="s">
         <v>26</v>
       </c>
       <c r="E497" s="32" t="s">
@@ -14723,12 +14847,12 @@
     <row x14ac:dyDescent="0.25" r="498" customHeight="1" ht="18.75">
       <c r="A498" s="29"/>
       <c r="B498" s="30" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="C498" s="30" t="s">
-        <v>238</v>
-      </c>
-      <c r="D498" s="52" t="s">
+        <v>241</v>
+      </c>
+      <c r="D498" s="55" t="s">
         <v>26</v>
       </c>
       <c r="E498" s="31" t="s">
@@ -14743,11 +14867,11 @@
     </row>
     <row x14ac:dyDescent="0.25" r="499" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A499" s="29" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="B499" s="30"/>
       <c r="C499" s="30"/>
-      <c r="D499" s="52"/>
+      <c r="D499" s="55"/>
       <c r="E499" s="3"/>
       <c r="F499" s="3"/>
       <c r="G499" s="3"/>
@@ -14759,12 +14883,12 @@
     <row x14ac:dyDescent="0.25" r="500" customHeight="1" ht="18.75">
       <c r="A500" s="29"/>
       <c r="B500" s="30" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="C500" s="30" t="s">
-        <v>951</v>
-      </c>
-      <c r="D500" s="78" t="s">
+        <v>954</v>
+      </c>
+      <c r="D500" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E500" s="41" t="s">
@@ -14772,20 +14896,20 @@
       </c>
       <c r="F500" s="4"/>
       <c r="G500" s="4"/>
-      <c r="H500" s="75"/>
-      <c r="I500" s="75"/>
+      <c r="H500" s="78"/>
+      <c r="I500" s="78"/>
       <c r="J500" s="11"/>
       <c r="K500" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="501" customHeight="1" ht="18.75">
       <c r="A501" s="29"/>
       <c r="B501" s="30" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="C501" s="30" t="s">
-        <v>953</v>
-      </c>
-      <c r="D501" s="52" t="s">
+        <v>956</v>
+      </c>
+      <c r="D501" s="55" t="s">
         <v>26</v>
       </c>
       <c r="E501" s="32" t="s">
@@ -14801,12 +14925,12 @@
     <row x14ac:dyDescent="0.25" r="502" customHeight="1" ht="18.75">
       <c r="A502" s="29"/>
       <c r="B502" s="30" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="C502" s="30" t="s">
-        <v>955</v>
-      </c>
-      <c r="D502" s="52" t="s">
+        <v>958</v>
+      </c>
+      <c r="D502" s="55" t="s">
         <v>26</v>
       </c>
       <c r="E502" s="32" t="s">
@@ -14821,11 +14945,11 @@
     </row>
     <row x14ac:dyDescent="0.25" r="503" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A503" s="29" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="B503" s="30"/>
       <c r="C503" s="30"/>
-      <c r="D503" s="52"/>
+      <c r="D503" s="55"/>
       <c r="E503" s="3"/>
       <c r="F503" s="3"/>
       <c r="G503" s="3"/>
@@ -14837,12 +14961,12 @@
     <row x14ac:dyDescent="0.25" r="504" customHeight="1" ht="18.75">
       <c r="A504" s="29"/>
       <c r="B504" s="30" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="C504" s="30" t="s">
-        <v>958</v>
-      </c>
-      <c r="D504" s="78" t="s">
+        <v>961</v>
+      </c>
+      <c r="D504" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E504" s="41" t="s">
@@ -14850,20 +14974,20 @@
       </c>
       <c r="F504" s="4"/>
       <c r="G504" s="4"/>
-      <c r="H504" s="75"/>
-      <c r="I504" s="75"/>
+      <c r="H504" s="78"/>
+      <c r="I504" s="78"/>
       <c r="J504" s="11"/>
       <c r="K504" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="505" customHeight="1" ht="18.75">
       <c r="A505" s="29"/>
       <c r="B505" s="30" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="C505" s="30" t="s">
-        <v>960</v>
-      </c>
-      <c r="D505" s="78" t="s">
+        <v>963</v>
+      </c>
+      <c r="D505" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E505" s="32" t="s">
@@ -14879,12 +15003,12 @@
     <row x14ac:dyDescent="0.25" r="506" customHeight="1" ht="18.75">
       <c r="A506" s="29"/>
       <c r="B506" s="30" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="C506" s="30" t="s">
-        <v>962</v>
-      </c>
-      <c r="D506" s="52" t="s">
+        <v>965</v>
+      </c>
+      <c r="D506" s="55" t="s">
         <v>26</v>
       </c>
       <c r="E506" s="32" t="s">
@@ -14899,11 +15023,11 @@
     </row>
     <row x14ac:dyDescent="0.25" r="507" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A507" s="29" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="B507" s="30"/>
       <c r="C507" s="30"/>
-      <c r="D507" s="52"/>
+      <c r="D507" s="55"/>
       <c r="E507" s="3"/>
       <c r="F507" s="3"/>
       <c r="G507" s="3"/>
@@ -14915,12 +15039,12 @@
     <row x14ac:dyDescent="0.25" r="508" customHeight="1" ht="18.75">
       <c r="A508" s="29"/>
       <c r="B508" s="30" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="C508" s="30" t="s">
-        <v>770</v>
-      </c>
-      <c r="D508" s="78" t="s">
+        <v>773</v>
+      </c>
+      <c r="D508" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E508" s="41" t="s">
@@ -14928,20 +15052,20 @@
       </c>
       <c r="F508" s="4"/>
       <c r="G508" s="4"/>
-      <c r="H508" s="44"/>
-      <c r="I508" s="44"/>
+      <c r="H508" s="47"/>
+      <c r="I508" s="47"/>
       <c r="J508" s="11"/>
       <c r="K508" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="509" customHeight="1" ht="18.75">
       <c r="A509" s="29"/>
       <c r="B509" s="30" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="C509" s="30" t="s">
-        <v>966</v>
-      </c>
-      <c r="D509" s="78" t="s">
+        <v>969</v>
+      </c>
+      <c r="D509" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E509" s="31" t="s">
@@ -14957,12 +15081,12 @@
     <row x14ac:dyDescent="0.25" r="510" customHeight="1" ht="18.75">
       <c r="A510" s="29"/>
       <c r="B510" s="30" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="C510" s="30" t="s">
-        <v>968</v>
-      </c>
-      <c r="D510" s="78" t="s">
+        <v>971</v>
+      </c>
+      <c r="D510" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E510" s="31" t="s">
@@ -14978,12 +15102,12 @@
     <row x14ac:dyDescent="0.25" r="511" customHeight="1" ht="18.75">
       <c r="A511" s="29"/>
       <c r="B511" s="30" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C511" s="30" t="s">
-        <v>970</v>
-      </c>
-      <c r="D511" s="52" t="s">
+        <v>973</v>
+      </c>
+      <c r="D511" s="55" t="s">
         <v>26</v>
       </c>
       <c r="E511" s="31" t="s">
@@ -14999,12 +15123,12 @@
     <row x14ac:dyDescent="0.25" r="512" customHeight="1" ht="18.75">
       <c r="A512" s="29"/>
       <c r="B512" s="30" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="C512" s="30" t="s">
-        <v>972</v>
-      </c>
-      <c r="D512" s="78" t="s">
+        <v>975</v>
+      </c>
+      <c r="D512" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E512" s="31" t="s">
@@ -15019,11 +15143,11 @@
     </row>
     <row x14ac:dyDescent="0.25" r="513" customHeight="1" ht="18.75">
       <c r="A513" s="24" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="B513" s="25"/>
       <c r="C513" s="25"/>
-      <c r="D513" s="79"/>
+      <c r="D513" s="82"/>
       <c r="E513" s="26"/>
       <c r="F513" s="4"/>
       <c r="G513" s="4"/>
@@ -15034,7 +15158,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="514" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A514" s="29" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="B514" s="30"/>
       <c r="C514" s="30"/>
@@ -15050,12 +15174,12 @@
     <row x14ac:dyDescent="0.25" r="515" customHeight="1" ht="18.75">
       <c r="A515" s="29"/>
       <c r="B515" s="30" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="C515" s="30" t="s">
-        <v>976</v>
-      </c>
-      <c r="D515" s="78" t="s">
+        <v>979</v>
+      </c>
+      <c r="D515" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E515" s="31" t="s">
@@ -15071,12 +15195,12 @@
     <row x14ac:dyDescent="0.25" r="516" customHeight="1" ht="18.75">
       <c r="A516" s="29"/>
       <c r="B516" s="30" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="C516" s="30" t="s">
-        <v>978</v>
-      </c>
-      <c r="D516" s="78" t="s">
+        <v>981</v>
+      </c>
+      <c r="D516" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E516" s="31" t="s">
@@ -15092,12 +15216,12 @@
     <row x14ac:dyDescent="0.25" r="517" customHeight="1" ht="18.75">
       <c r="A517" s="29"/>
       <c r="B517" s="30" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="C517" s="30" t="s">
-        <v>980</v>
-      </c>
-      <c r="D517" s="78" t="s">
+        <v>983</v>
+      </c>
+      <c r="D517" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E517" s="31" t="s">
@@ -15113,12 +15237,12 @@
     <row x14ac:dyDescent="0.25" r="518" customHeight="1" ht="18.75">
       <c r="A518" s="29"/>
       <c r="B518" s="30" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="C518" s="30" t="s">
-        <v>982</v>
-      </c>
-      <c r="D518" s="78" t="s">
+        <v>985</v>
+      </c>
+      <c r="D518" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E518" s="31" t="s">
@@ -15134,12 +15258,12 @@
     <row x14ac:dyDescent="0.25" r="519" customHeight="1" ht="18.75">
       <c r="A519" s="29"/>
       <c r="B519" s="30" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="C519" s="30" t="s">
-        <v>984</v>
-      </c>
-      <c r="D519" s="78" t="s">
+        <v>987</v>
+      </c>
+      <c r="D519" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E519" s="31" t="s">
@@ -15155,12 +15279,12 @@
     <row x14ac:dyDescent="0.25" r="520" customHeight="1" ht="18.75">
       <c r="A520" s="29"/>
       <c r="B520" s="30" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="C520" s="30" t="s">
-        <v>986</v>
-      </c>
-      <c r="D520" s="78" t="s">
+        <v>989</v>
+      </c>
+      <c r="D520" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E520" s="31" t="s">
@@ -15175,10 +15299,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="521" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A521" s="24" t="s">
-        <v>987</v>
-      </c>
-      <c r="B521" s="80" t="s">
-        <v>988</v>
+        <v>990</v>
+      </c>
+      <c r="B521" s="83" t="s">
+        <v>991</v>
       </c>
       <c r="C521" s="39"/>
       <c r="D521" s="39"/>
@@ -15192,7 +15316,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="522" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A522" s="29" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="B522" s="30"/>
       <c r="C522" s="30"/>
@@ -15208,12 +15332,12 @@
     <row x14ac:dyDescent="0.25" r="523" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A523" s="30"/>
       <c r="B523" s="30" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="C523" s="30" t="s">
-        <v>991</v>
-      </c>
-      <c r="D523" s="78" t="s">
+        <v>994</v>
+      </c>
+      <c r="D523" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E523" s="30" t="s">
@@ -15229,12 +15353,12 @@
     <row x14ac:dyDescent="0.25" r="524" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A524" s="30"/>
       <c r="B524" s="30" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="C524" s="30" t="s">
-        <v>993</v>
-      </c>
-      <c r="D524" s="52" t="s">
+        <v>996</v>
+      </c>
+      <c r="D524" s="55" t="s">
         <v>26</v>
       </c>
       <c r="E524" s="30" t="s">
@@ -15250,12 +15374,12 @@
     <row x14ac:dyDescent="0.25" r="525" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A525" s="30"/>
       <c r="B525" s="30" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="C525" s="30" t="s">
-        <v>995</v>
-      </c>
-      <c r="D525" s="78" t="s">
+        <v>998</v>
+      </c>
+      <c r="D525" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E525" s="30" t="s">
@@ -15271,12 +15395,12 @@
     <row x14ac:dyDescent="0.25" r="526" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A526" s="30"/>
       <c r="B526" s="30" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="C526" s="30" t="s">
-        <v>997</v>
-      </c>
-      <c r="D526" s="78" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D526" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E526" s="30" t="s">
@@ -15292,12 +15416,12 @@
     <row x14ac:dyDescent="0.25" r="527" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A527" s="30"/>
       <c r="B527" s="30" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="C527" s="30" t="s">
-        <v>999</v>
-      </c>
-      <c r="D527" s="52" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D527" s="55" t="s">
         <v>26</v>
       </c>
       <c r="E527" s="30" t="s">
@@ -15313,12 +15437,12 @@
     <row x14ac:dyDescent="0.25" r="528" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A528" s="30"/>
       <c r="B528" s="30" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="C528" s="30" t="s">
-        <v>1001</v>
-      </c>
-      <c r="D528" s="78" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D528" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E528" s="30" t="s">
@@ -15334,12 +15458,12 @@
     <row x14ac:dyDescent="0.25" r="529" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A529" s="29"/>
       <c r="B529" s="30" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="C529" s="30" t="s">
-        <v>1003</v>
-      </c>
-      <c r="D529" s="52" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D529" s="55" t="s">
         <v>26</v>
       </c>
       <c r="E529" s="30" t="s">
@@ -15355,12 +15479,12 @@
     <row x14ac:dyDescent="0.25" r="530" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A530" s="29"/>
       <c r="B530" s="30" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="C530" s="30" t="s">
-        <v>1005</v>
-      </c>
-      <c r="D530" s="78" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D530" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E530" s="30" t="s">
@@ -15376,12 +15500,12 @@
     <row x14ac:dyDescent="0.25" r="531" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A531" s="29"/>
       <c r="B531" s="30" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="C531" s="30" t="s">
-        <v>1007</v>
-      </c>
-      <c r="D531" s="78" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D531" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E531" s="30" t="s">
@@ -15397,12 +15521,12 @@
     <row x14ac:dyDescent="0.25" r="532" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A532" s="29"/>
       <c r="B532" s="30" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="C532" s="30" t="s">
-        <v>1009</v>
-      </c>
-      <c r="D532" s="78" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D532" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E532" s="30" t="s">
@@ -15418,12 +15542,12 @@
     <row x14ac:dyDescent="0.25" r="533" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A533" s="29"/>
       <c r="B533" s="30" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="C533" s="30" t="s">
-        <v>1011</v>
-      </c>
-      <c r="D533" s="78" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D533" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E533" s="30" t="s">
@@ -15439,12 +15563,12 @@
     <row x14ac:dyDescent="0.25" r="534" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A534" s="29"/>
       <c r="B534" s="30" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="C534" s="30" t="s">
-        <v>1013</v>
-      </c>
-      <c r="D534" s="78" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D534" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E534" s="30" t="s">
@@ -15460,12 +15584,12 @@
     <row x14ac:dyDescent="0.25" r="535" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A535" s="29"/>
       <c r="B535" s="30" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="C535" s="30" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D535" s="78" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D535" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E535" s="30" t="s">
@@ -15481,12 +15605,12 @@
     <row x14ac:dyDescent="0.25" r="536" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A536" s="29"/>
       <c r="B536" s="30" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="C536" s="30" t="s">
-        <v>1017</v>
-      </c>
-      <c r="D536" s="78" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D536" s="81" t="s">
         <v>26</v>
       </c>
       <c r="E536" s="30" t="s">
@@ -15503,7 +15627,7 @@
       <c r="A537" s="39"/>
       <c r="B537" s="39"/>
       <c r="C537" s="39"/>
-      <c r="D537" s="79"/>
+      <c r="D537" s="82"/>
       <c r="E537" s="39"/>
       <c r="F537" s="3"/>
       <c r="G537" s="3"/>
@@ -15514,7 +15638,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="538" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A538" s="29" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="B538" s="3"/>
       <c r="C538" s="3"/>
@@ -15528,8 +15652,8 @@
       <c r="K538" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="539" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A539" s="81" t="s">
-        <v>1019</v>
+      <c r="A539" s="84" t="s">
+        <v>1022</v>
       </c>
       <c r="B539" s="3"/>
       <c r="C539" s="3"/>
@@ -15537,21 +15661,21 @@
       <c r="E539" s="3"/>
       <c r="F539" s="3"/>
       <c r="G539" s="3"/>
-      <c r="H539" s="81"/>
-      <c r="I539" s="81"/>
+      <c r="H539" s="84"/>
+      <c r="I539" s="84"/>
       <c r="J539" s="4"/>
       <c r="K539" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="540" customHeight="1" ht="18.75">
       <c r="A540" s="39"/>
-      <c r="B540" s="61"/>
-      <c r="C540" s="61"/>
-      <c r="D540" s="62"/>
-      <c r="E540" s="62"/>
+      <c r="B540" s="64"/>
+      <c r="C540" s="64"/>
+      <c r="D540" s="65"/>
+      <c r="E540" s="65"/>
       <c r="F540" s="4"/>
       <c r="G540" s="4"/>
-      <c r="H540" s="62"/>
-      <c r="I540" s="62"/>
+      <c r="H540" s="65"/>
+      <c r="I540" s="65"/>
       <c r="J540" s="11"/>
       <c r="K540" s="11"/>
     </row>
@@ -15569,59 +15693,59 @@
       <c r="K541" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="542" customHeight="1" ht="18.75">
-      <c r="A542" s="82" t="s">
-        <v>1020</v>
-      </c>
-      <c r="B542" s="83" t="s">
-        <v>1021</v>
-      </c>
-      <c r="C542" s="84"/>
-      <c r="D542" s="84"/>
-      <c r="E542" s="85"/>
+      <c r="A542" s="85" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B542" s="86" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C542" s="87"/>
+      <c r="D542" s="87"/>
+      <c r="E542" s="88"/>
       <c r="F542" s="4"/>
       <c r="G542" s="4"/>
-      <c r="H542" s="86"/>
-      <c r="I542" s="86"/>
+      <c r="H542" s="89"/>
+      <c r="I542" s="89"/>
       <c r="J542" s="11"/>
       <c r="K542" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="543" customHeight="1" ht="18.75">
-      <c r="A543" s="87" t="s">
-        <v>1022</v>
-      </c>
-      <c r="B543" s="86" t="s">
-        <v>1023</v>
+      <c r="A543" s="90" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B543" s="89" t="s">
+        <v>1026</v>
       </c>
       <c r="C543" s="13"/>
       <c r="D543" s="13"/>
-      <c r="E543" s="88"/>
+      <c r="E543" s="91"/>
       <c r="F543" s="4"/>
       <c r="G543" s="4"/>
-      <c r="H543" s="86"/>
-      <c r="I543" s="86"/>
+      <c r="H543" s="89"/>
+      <c r="I543" s="89"/>
       <c r="J543" s="11"/>
       <c r="K543" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="544" customHeight="1" ht="18.75">
-      <c r="A544" s="89" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B544" s="90" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C544" s="91"/>
-      <c r="D544" s="91"/>
-      <c r="E544" s="92"/>
+      <c r="A544" s="92" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B544" s="93" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C544" s="94"/>
+      <c r="D544" s="94"/>
+      <c r="E544" s="95"/>
       <c r="F544" s="4"/>
       <c r="G544" s="4"/>
-      <c r="H544" s="86"/>
-      <c r="I544" s="86"/>
+      <c r="H544" s="89"/>
+      <c r="I544" s="89"/>
       <c r="J544" s="11"/>
       <c r="K544" s="11"/>
     </row>
     <row x14ac:dyDescent="0.25" r="545" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A545" s="24" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="B545" s="3"/>
       <c r="C545" s="3"/>
